--- a/Digitised_Records_High_Frequency.xlsx
+++ b/Digitised_Records_High_Frequency.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B29375F9-FC14-419A-919F-BDE098E746F4}"/>
+  <xr:revisionPtr revIDLastSave="561" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37027FED-D32D-44BF-9301-6F9CF198235F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="420">
   <si>
     <t>Location</t>
   </si>
@@ -401,9 +401,6 @@
     <t>1893-1913, 1943-1955</t>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S002216941201092X#s0010</t>
-  </si>
-  <si>
     <t>La Rochelle, Vieux Port</t>
   </si>
   <si>
@@ -782,43 +779,7 @@
     <t>Dún Laoghaire Harbour</t>
   </si>
   <si>
-    <t>Sacramento River, I Street</t>
-  </si>
-  <si>
-    <t>Sacramento River, Snodgrass</t>
-  </si>
-  <si>
-    <t>Mokelumne River, Thornton</t>
-  </si>
-  <si>
-    <t>Sacramento River, Walnut Grove</t>
-  </si>
-  <si>
-    <t>Mokelumne River, New Hope</t>
-  </si>
-  <si>
-    <t>Sacramento River, Rio Vista</t>
-  </si>
-  <si>
-    <t>Georgiana Slough, Mokelumne River</t>
-  </si>
-  <si>
-    <t>Three Mile Slough, Sacramento River</t>
-  </si>
-  <si>
-    <t>Sacramento River, Collinsville</t>
-  </si>
-  <si>
     <t>Suisun Bay, Benicia (East Bay, Martinez)</t>
-  </si>
-  <si>
-    <t>Old River, Rock Slough (Old River, Bacon Island)</t>
-  </si>
-  <si>
-    <t>San Joaquin River, Burns Cutoff (Stockton)</t>
-  </si>
-  <si>
-    <t>Middle River, Borden (Union Pt)</t>
   </si>
   <si>
     <t xml:space="preserve">Georges and Princes Pier </t>
@@ -1064,141 +1025,9 @@
     <t>UnGraph</t>
   </si>
   <si>
-    <t>https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf</t>
-  </si>
-  <si>
-    <t>https://journals.ametsoc.org/view/journals/clim/16/6/1520-0442_2003_016_0982_svatcc_2.0.co_2.xml</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2003GL019166</t>
-  </si>
-  <si>
-    <t>https://academic.oup.com/gji/article/71/3/809/656230?login=true</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s10236-005-0056-8</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s10236-005-0044-z</t>
-  </si>
-  <si>
-    <t>https://journals.ametsoc.org/view/journals/phoc/36/6/jpo2876.1.xml</t>
-  </si>
-  <si>
-    <t>https://journals.openedition.org/mediterranee/170#tocto1n3</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S0278434306003888#sec2</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S0278434309002313</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006404</t>
-  </si>
-  <si>
     <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006113</t>
   </si>
   <si>
-    <t>https://academic.oup.com/gji/article/182/2/781/571033</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JC007558</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/doi/abs/10.2989/1814232X.2012.689623?casa_token=zBny8ik3tAMAAAAA:D-WLZrlhXskUGl1Xag8khGwd83rNrPI2GZ94RlKOsCvfW4t4DDubKDq8PhmhPgZCerNLRIoGbCBZ</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JF001964</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S0278434313001283#s0010</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s10236-013-0598-0</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s00190-014-0728-6</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010</t>
-  </si>
-  <si>
-    <t>https://refmar.shom.fr/sites/default/files/2024-07/Reconstruction%20serie%20maregraphique%20Saint-Nazaire%20par%20Yann%20Ferret%202016.pdf</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2016GL069494</t>
-  </si>
-  <si>
-    <t>https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2018JC014313</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s12237-018-0379-6</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s00190-019-01238-w#Sec2</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015656</t>
-  </si>
-  <si>
-    <t>https://theses.hal.science/tel-02899411/</t>
-  </si>
-  <si>
-    <t>https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112</t>
-  </si>
-  <si>
-    <t>https://southerncoastalgroup-scopac.org.uk/wp-content/uploads/2022/01/Digitisation-and-Analysis-of-Poole-Harbour-Tide-Gauge-Record-September-2021.pdf</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328</t>
-  </si>
-  <si>
-    <t>https://os.copernicus.org/articles/17/1623/2021/#section2</t>
-  </si>
-  <si>
-    <t>https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals</t>
-  </si>
-  <si>
-    <t>https://hal.science/hal-04555208v1/file/Khan2023.pdf</t>
-  </si>
-  <si>
-    <t>https://www.scirp.org/journal/paperinformation?paperid=128406</t>
-  </si>
-  <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908</t>
-  </si>
-  <si>
-    <t>https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.256</t>
-  </si>
-  <si>
-    <t>https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018</t>
-  </si>
-  <si>
-    <t>https://hgss.copernicus.org/articles/17/1/2026/</t>
-  </si>
-  <si>
-    <t>https://www.zooniverse.org/projects/psmsl/uk-tides</t>
-  </si>
-  <si>
     <t>Resolution</t>
   </si>
   <si>
@@ -1323,6 +1152,174 @@
   </si>
   <si>
     <t>San Joaquin River (Antioch)</t>
+  </si>
+  <si>
+    <t>Sacramento River (I Street)</t>
+  </si>
+  <si>
+    <t>Sacramento River (Snodgrass)</t>
+  </si>
+  <si>
+    <t>Mokelumne River (Thornton)</t>
+  </si>
+  <si>
+    <t>Sacramento River (Walnut Grove)</t>
+  </si>
+  <si>
+    <t>Mokelumne River (New Hope)</t>
+  </si>
+  <si>
+    <t>Sacramento River (Rio Vista)</t>
+  </si>
+  <si>
+    <t>Georgiana Slough (Mokelumne River)</t>
+  </si>
+  <si>
+    <t>Three Mile Slough (Sacramento River)</t>
+  </si>
+  <si>
+    <t>Sacramento River (Collinsville)</t>
+  </si>
+  <si>
+    <t>Old River (Rock Slough), (Old River, Bacon Island)</t>
+  </si>
+  <si>
+    <t>San Joaquin River (Burns Cutoff, Stockton)</t>
+  </si>
+  <si>
+    <t>Middle River (Borden, Union Pt)</t>
+  </si>
+  <si>
+    <t>comparison of recent and historical tides and mean sea-levels off Ireland | Geophysical Journal International | Oxford Academic</t>
+  </si>
+  <si>
+    <t>ESM13/4</t>
+  </si>
+  <si>
+    <t>Storminess Variability along the California Coast: 1858–2000 in: Journal of Climate Volume 16 Issue 6 (2003)</t>
+  </si>
+  <si>
+    <t>An updated analysis of long‐term sea level change in New Zealand - Hannah - 2004 - Geophysical Research Letters - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Tales of the Venerable Honolulu Tide Gauge in: Journal of Physical Oceanography Volume 36 Issue 6 (2006)</t>
+  </si>
+  <si>
+    <t>Extreme sea levels in two northern Mediterranean areas</t>
+  </si>
+  <si>
+    <t>Sea surges in Camargue: Trends over the 20th century - ScienceDirect</t>
+  </si>
+  <si>
+    <t>Mean sea level trends around the English Channel over the 20th century and their wider context - ScienceDirect</t>
+  </si>
+  <si>
+    <t>Sea level at Saint Paul Island, southern Indian Ocean, from 1874 to the present - Testut - 2010 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Twentieth century constraints on sea level change and earthquake deformation at Macquarie Island | Geophysical Journal International | Oxford Academic</t>
+  </si>
+  <si>
+    <t>The long sea level record at Cadiz (southern Spain) from 1880 to 2009 - Marcos - 2011 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Sea level changes at Ascension Island in the last half century: African Journal of Marine Science: Vol 34, No 3</t>
+  </si>
+  <si>
+    <t>Refined numerical modeling of the 1979 tsunami in Nice (French Riviera): Comparison with coastal data - Labbé - 2012 - Journal of Geophysical Research: Earth Surface - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Sea level changes at Tenerife Island (NE Tropical Atlantic) since 1927 - Marcos - 2013 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Reconstruction of a two-century long sea level record for the Pertuis d’Antioche (France) - ScienceDirect</t>
+  </si>
+  <si>
+    <t>Increasing storm tides in New York Harbor, 1844–2013 - Talke - 2014 - Geophysical Research Letters - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>(PDF) Maintaining legacy data: Saving Belfast Harbour (UK) tide-gauge data (1901–2010)</t>
+  </si>
+  <si>
+    <t>27-2016 Rapport_Final_Reconstruction_serie_SaintNazaire</t>
+  </si>
+  <si>
+    <t>The effect of channel deepening on tides and storm surge: A case study of Wilmington, NC - Familkhalili - 2016 - Geophysical Research Letters - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Archival Water-Level Measurements: Recovering Historical Data to Help Design for the Future</t>
+  </si>
+  <si>
+    <t>Relative Sea Level, Tides, and Extreme Water Levels in Boston Harbor From 1825 to 2018 - Talke - 2018 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Bigger Tides, Less Flooding: Effects of Dredging on Barotropic Dynamics in a Highly Modified Estuary - Ralston - 2019 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Nineteenth‐Century Tides in the Gulf of Maine and Implications for Secular Trends - Ray - 2019 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Historical tide gauge sea‐level observations in Alicante and Santander (Spain) since the 19th century - Marcos - 2021 - Geoscience Data Journal - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Digitisation and Analysis of Poole Harbour Tide Gauge Record</t>
+  </si>
+  <si>
+    <t>The Influence of Channel Deepening on Tides, River Discharge Effects, and Storm Surge - Talke - 2021 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>OS - Mean sea level and tidal change in Ireland since 1842: a case study of Cork</t>
+  </si>
+  <si>
+    <t>Digitising historical sea level records in the Thames Estuary, UK - ProQuest</t>
+  </si>
+  <si>
+    <t>Extension of a high temporal resolution sea level time series at Socoa (Saint-Jean-de-Luz, France) back to 1875</t>
+  </si>
+  <si>
+    <t>Evolutive Trend of Water Level in the Ebrie Lagoon by Reconstitution of the Tide Gauge Time Series in Front of the Abidjan Coastline (Côte d’Ivoire)</t>
+  </si>
+  <si>
+    <t>Digitizing the Williamstown, Australia Tide‐Gauge Record Back to 1872: Insights Into Changing Extremes - McInnes - 2024 - Journal of Geophysical Research: Oceans - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>The accurate digitization of historical sea level records - McLoughlin - 2024 - Geoscience Data Journal - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Recovery of Daily Water Levels in the Sacramento‐San Joaquin Delta, 1915–2023 - Lee - 2025 - Geoscience Data Journal - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>HGSS - Three historic tide gauge records from Svalbard</t>
+  </si>
+  <si>
+    <t>(PDF) Nineteenth Century North American and Pacific Tidal Data: Lost or Just Forgotten?</t>
+  </si>
+  <si>
+    <t>Brest sea level record: a time series construction back to the early eighteenth century | Ocean Dynamics | Springer Nature Link</t>
+  </si>
+  <si>
+    <t>Rescue of the historical sea level record of Marseille (France) from 1885 to 1988 and its extension back to 1849–1851 | Journal of Geodesy | Springer Nature Link</t>
+  </si>
+  <si>
+    <t>Impact of Channel Deepening on Tidal and Gravitational Circulation in a Highly Engineered Estuarine Basin | Estuaries and Coasts | Springer Nature Link</t>
+  </si>
+  <si>
+    <t>Influence of morphological changes of the foreshore on the hydrodynamics and evolution of the Hauts-de-France coastline since the nineteenth century - TEL - Online theses</t>
+  </si>
+  <si>
+    <t>The sea level at Port-aux-Français, Kerguelen Island, from 1949 to the present | Ocean Dynamics | Springer Nature Link</t>
+  </si>
+  <si>
+    <t>Characteristics of intra-, inter-annual and decadal sea-level variability and the role of meteorological forcing: the long record of Cuxhaven | Ocean Dynamics | Springer Nature Link</t>
+  </si>
+  <si>
+    <t>Rescue of the 1873–1922 high and low waters of the Porto Corsini/Marina di Ravenna (northern Adriatic, Italy) tide gauge | Journal of Geodesy | Springer Nature Link</t>
+  </si>
+  <si>
+    <t>Analysing the 100 year sea level record of Leixões, Portugal - ScienceDirect</t>
+  </si>
+  <si>
+    <t>UK Tides | Zooniverse - People-powered research</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1493,15 +1490,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1519,14 +1510,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1546,6 +1532,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1865,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89AE8008-17FD-4F1A-998F-46D82FC2937F}">
-  <dimension ref="A1:U255"/>
+  <dimension ref="A1:R255"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.36328125" style="3" bestFit="1" customWidth="1"/>
@@ -1879,8 +1869,8 @@
     <col min="10" max="10" width="18.90625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="157.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.7265625" style="3"/>
+    <col min="13" max="13" width="169.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1903,13 +1893,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -1917,8 +1907,8 @@
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="26" t="s">
-        <v>379</v>
+      <c r="L1" s="23" t="s">
+        <v>322</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -1944,7 +1934,7 @@
         <v>1913</v>
       </c>
       <c r="G2" s="4">
-        <f>(1+(F2-E2))-I2</f>
+        <f t="shared" ref="G2:G37" si="0">(1+(F2-E2))-I2</f>
         <v>1.375</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -1955,7 +1945,7 @@
         <v>0.625</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>21</v>
@@ -1964,14 +1954,14 @@
         <v>21</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="4">
@@ -1987,7 +1977,7 @@
         <v>2013</v>
       </c>
       <c r="G3" s="4">
-        <f>(1+(F3-E3))-I3</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -1997,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>21</v>
@@ -2005,15 +1995,15 @@
       <c r="L3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>353</v>
+      <c r="M3" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="4">
@@ -2029,7 +2019,7 @@
         <v>2013</v>
       </c>
       <c r="G4" s="4">
-        <f>(1+(F4-E4))-I4</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -2039,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>21</v>
@@ -2047,15 +2037,15 @@
       <c r="L4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>353</v>
+      <c r="M4" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="23" t="s">
+      <c r="A5" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="4">
@@ -2071,7 +2061,7 @@
         <v>2013</v>
       </c>
       <c r="G5" s="4">
-        <f>(1+(F5-E5))-I5</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -2081,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>21</v>
@@ -2089,15 +2079,15 @@
       <c r="L5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>353</v>
+      <c r="M5" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="4">
@@ -2113,7 +2103,7 @@
         <v>2013</v>
       </c>
       <c r="G6" s="4">
-        <f>(1+(F6-E6))-I6</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -2123,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>21</v>
@@ -2131,15 +2121,15 @@
       <c r="L6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>353</v>
+      <c r="M6" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="4">
@@ -2155,17 +2145,17 @@
         <v>2013</v>
       </c>
       <c r="G7" s="4">
-        <f>(1+(F7-E7))-I7</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="I7" s="4">
         <v>9</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>21</v>
@@ -2173,13 +2163,13 @@
       <c r="L7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>353</v>
+      <c r="M7" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
@@ -2197,31 +2187,31 @@
         <v>1965</v>
       </c>
       <c r="G8" s="4">
-        <f>(1+(F8-E8))-I8</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="I8" s="4">
         <v>4</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>374</v>
+      <c r="M8" s="6" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2239,17 +2229,17 @@
         <v>1966</v>
       </c>
       <c r="G9" s="4">
-        <f>(1+(F9-E9))-I9</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="I9" s="4">
         <v>4</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>9</v>
@@ -2257,8 +2247,8 @@
       <c r="L9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>374</v>
+      <c r="M9" s="6" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -2281,7 +2271,7 @@
         <v>1970</v>
       </c>
       <c r="G10" s="4">
-        <f>(1+(F10-E10))-I10</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -2291,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>9</v>
@@ -2300,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -2323,7 +2313,7 @@
         <v>1936</v>
       </c>
       <c r="G11" s="4">
-        <f>(1+(F11-E11))-I11</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -2333,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>9</v>
@@ -2342,7 +2332,7 @@
         <v>15</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -2365,7 +2355,7 @@
         <v>1943</v>
       </c>
       <c r="G12" s="4">
-        <f>(1+(F12-E12))-I12</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H12" s="3" t="s">
@@ -2375,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>9</v>
@@ -2384,7 +2374,7 @@
         <v>15</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -2407,7 +2397,7 @@
         <v>1943</v>
       </c>
       <c r="G13" s="4">
-        <f>(1+(F13-E13))-I13</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H13" s="3" t="s">
@@ -2417,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>9</v>
@@ -2426,7 +2416,7 @@
         <v>15</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -2449,7 +2439,7 @@
         <v>1944</v>
       </c>
       <c r="G14" s="4">
-        <f>(1+(F14-E14))-I14</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H14" s="3" t="s">
@@ -2459,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>9</v>
@@ -2468,7 +2458,7 @@
         <v>15</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -2491,7 +2481,7 @@
         <v>1944</v>
       </c>
       <c r="G15" s="4">
-        <f>(1+(F15-E15))-I15</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H15" s="3" t="s">
@@ -2501,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>9</v>
@@ -2510,7 +2500,7 @@
         <v>15</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -2533,7 +2523,7 @@
         <v>1944</v>
       </c>
       <c r="G16" s="4">
-        <f>(1+(F16-E16))-I16</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H16" s="3" t="s">
@@ -2543,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>9</v>
@@ -2552,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -2575,7 +2565,7 @@
         <v>1968</v>
       </c>
       <c r="G17" s="4">
-        <f>(1+(F17-E17))-I17</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="H17" s="3" t="s">
@@ -2585,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>9</v>
@@ -2594,7 +2584,7 @@
         <v>15</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -2617,7 +2607,7 @@
         <v>1968</v>
       </c>
       <c r="G18" s="4">
-        <f>(1+(F18-E18))-I18</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="H18" s="3" t="s">
@@ -2627,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>9</v>
@@ -2636,7 +2626,7 @@
         <v>15</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -2659,7 +2649,7 @@
         <v>1967</v>
       </c>
       <c r="G19" s="4">
-        <f>(1+(F19-E19))-I19</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="H19" s="3" t="s">
@@ -2669,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>9</v>
@@ -2678,7 +2668,7 @@
         <v>15</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -2701,7 +2691,7 @@
         <v>1964</v>
       </c>
       <c r="G20" s="4">
-        <f>(1+(F20-E20))-I20</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
@@ -2711,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>9</v>
@@ -2720,7 +2710,7 @@
         <v>15</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -2743,7 +2733,7 @@
         <v>1961</v>
       </c>
       <c r="G21" s="4">
-        <f>(1+(F21-E21))-I21</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H21" s="3" t="s">
@@ -2753,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>9</v>
@@ -2762,7 +2752,7 @@
         <v>15</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -2785,7 +2775,7 @@
         <v>1968</v>
       </c>
       <c r="G22" s="4">
-        <f>(1+(F22-E22))-I22</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="H22" s="3" t="s">
@@ -2795,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>9</v>
@@ -2804,7 +2794,7 @@
         <v>15</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -2827,7 +2817,7 @@
         <v>1949</v>
       </c>
       <c r="G23" s="4">
-        <f>(1+(F23-E23))-I23</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="H23" s="3" t="s">
@@ -2837,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>9</v>
@@ -2846,7 +2836,7 @@
         <v>15</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -2869,7 +2859,7 @@
         <v>1842</v>
       </c>
       <c r="G24" s="4">
-        <f>(1+(F24-E24))-I24</f>
+        <f t="shared" si="0"/>
         <v>0.60301163586584527</v>
       </c>
       <c r="H24" s="3" t="s">
@@ -2880,7 +2870,7 @@
         <v>0.39698836413415467</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>9</v>
@@ -2889,7 +2879,7 @@
         <v>79</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -2912,7 +2902,7 @@
         <v>1955</v>
       </c>
       <c r="G25" s="4">
-        <f>(1+(F25-E25))-I25</f>
+        <f t="shared" si="0"/>
         <v>8.0082135523613984E-2</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -2923,7 +2913,7 @@
         <v>0.91991786447638602</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>9</v>
@@ -2931,8 +2921,8 @@
       <c r="L25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M25" s="5" t="s">
-        <v>348</v>
+      <c r="M25" s="6" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -2955,7 +2945,7 @@
         <v>1994</v>
       </c>
       <c r="G26" s="4">
-        <f>(1+(F26-E26))-I26</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="H26" s="3" t="s">
@@ -2965,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>9</v>
@@ -2974,7 +2964,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -2997,7 +2987,7 @@
         <v>1979</v>
       </c>
       <c r="G27" s="4">
-        <f>(1+(F27-E27))-I27</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="H27" s="3" t="s">
@@ -3007,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>9</v>
@@ -3016,7 +3006,7 @@
         <v>15</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -3039,7 +3029,7 @@
         <v>1979</v>
       </c>
       <c r="G28" s="4">
-        <f>(1+(F28-E28))-I28</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="H28" s="3" t="s">
@@ -3049,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>9</v>
@@ -3058,7 +3048,7 @@
         <v>15</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -3081,7 +3071,7 @@
         <v>1948</v>
       </c>
       <c r="G29" s="4">
-        <f>(1+(F29-E29))-I29</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="H29" s="3" t="s">
@@ -3091,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>9</v>
@@ -3100,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -3123,7 +3113,7 @@
         <v>1991</v>
       </c>
       <c r="G30" s="4">
-        <f>(1+(F30-E30))-I30</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="H30" s="3" t="s">
@@ -3134,7 +3124,7 @@
         <v>14</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>9</v>
@@ -3143,7 +3133,7 @@
         <v>15</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -3166,7 +3156,7 @@
         <v>1966</v>
       </c>
       <c r="G31" s="4">
-        <f>(1+(F31-E31))-I31</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="H31" s="3" t="s">
@@ -3176,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>9</v>
@@ -3185,7 +3175,7 @@
         <v>15</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -3208,7 +3198,7 @@
         <v>1998</v>
       </c>
       <c r="G32" s="4">
-        <f>(1+(F32-E32))-I32</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H32" s="3" t="s">
@@ -3218,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>9</v>
@@ -3227,7 +3217,7 @@
         <v>15</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -3250,7 +3240,7 @@
         <v>1679</v>
       </c>
       <c r="G33" s="4">
-        <f>(1+(F33-E33))-I33</f>
+        <f t="shared" si="0"/>
         <v>2.1902806297056765E-2</v>
       </c>
       <c r="H33" s="3" t="s">
@@ -3261,7 +3251,7 @@
         <v>0.97809719370294324</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>9</v>
@@ -3270,7 +3260,7 @@
         <v>21</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>339</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -3293,7 +3283,7 @@
         <v>1716</v>
       </c>
       <c r="G34" s="4">
-        <f>(1+(F34-E34))-I34</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="H34" s="3" t="s">
@@ -3303,7 +3293,7 @@
         <v>18</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>9</v>
@@ -3312,7 +3302,7 @@
         <v>79</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>339</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -3335,7 +3325,7 @@
         <v>1832</v>
       </c>
       <c r="G35" s="4">
-        <f>(1+(F35-E35))-I35</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="H35" s="3" t="s">
@@ -3346,7 +3336,7 @@
         <v>32</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>9</v>
@@ -3355,12 +3345,12 @@
         <v>79</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>339</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -3378,7 +3368,7 @@
         <v>2008</v>
       </c>
       <c r="G36" s="4">
-        <f>(1+(F36-E36))-I36</f>
+        <f t="shared" si="0"/>
         <v>119</v>
       </c>
       <c r="H36" s="3" t="s">
@@ -3388,7 +3378,7 @@
         <v>44</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>9</v>
@@ -3396,13 +3386,13 @@
       <c r="L36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M36" s="25" t="s">
-        <v>339</v>
+      <c r="M36" s="6" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -3420,7 +3410,7 @@
         <v>1812</v>
       </c>
       <c r="G37" s="4">
-        <f>(1+(F37-E37))-I37</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="H37" s="3" t="s">
@@ -3430,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>9</v>
@@ -3438,15 +3428,15 @@
       <c r="L37" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M37" s="25" t="s">
-        <v>339</v>
+      <c r="M37" s="6" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="7">
@@ -3471,7 +3461,7 @@
         <v>1.06</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>91</v>
@@ -3480,14 +3470,14 @@
         <v>15</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>341</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="7">
@@ -3512,7 +3502,7 @@
         <v>0.35</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>91</v>
@@ -3520,15 +3510,15 @@
       <c r="L39" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="32" t="s">
-        <v>341</v>
+      <c r="M39" s="6" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="7">
@@ -3553,7 +3543,7 @@
         <v>3</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>91</v>
@@ -3561,8 +3551,8 @@
       <c r="L40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M40" s="32" t="s">
-        <v>342</v>
+      <c r="M40" s="6" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -3585,7 +3575,7 @@
         <v>1874</v>
       </c>
       <c r="G41" s="4">
-        <f>(1+(F41-E41))-I41</f>
+        <f t="shared" ref="G41:G73" si="1">(1+(F41-E41))-I41</f>
         <v>1</v>
       </c>
       <c r="H41" s="3" t="s">
@@ -3595,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>9</v>
@@ -3603,8 +3593,8 @@
       <c r="L41" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M41" s="31" t="s">
-        <v>344</v>
+      <c r="M41" s="6" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
@@ -3627,7 +3617,7 @@
         <v>1979</v>
       </c>
       <c r="G42" s="4">
-        <f>(1+(F42-E42))-I42</f>
+        <f t="shared" si="1"/>
         <v>2.739726027397249E-3</v>
       </c>
       <c r="H42" s="3" t="s">
@@ -3638,7 +3628,7 @@
         <v>0.99726027397260275</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>91</v>
@@ -3646,8 +3636,8 @@
       <c r="L42" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="M42" s="32" t="s">
-        <v>349</v>
+      <c r="M42" s="6" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
@@ -3670,7 +3660,7 @@
         <v>1979</v>
       </c>
       <c r="G43" s="4">
-        <f>(1+(F43-E43))-I43</f>
+        <f t="shared" si="1"/>
         <v>2.739726027397249E-3</v>
       </c>
       <c r="H43" s="3" t="s">
@@ -3681,7 +3671,7 @@
         <v>0.99726027397260275</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>91</v>
@@ -3689,15 +3679,15 @@
       <c r="L43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="M43" s="32" t="s">
-        <v>349</v>
+      <c r="M43" s="6" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A44" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B44" s="23" t="s">
+      <c r="A44" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="4">
@@ -3713,17 +3703,17 @@
         <v>1892</v>
       </c>
       <c r="G44" s="4">
-        <f>(1+(F44-E44))-I44</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="I44" s="4">
         <v>39</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>9</v>
@@ -3732,14 +3722,14 @@
         <v>15</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A45" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="B45" s="23" t="s">
+      <c r="A45" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="4">
@@ -3755,18 +3745,18 @@
         <v>1997</v>
       </c>
       <c r="G45" s="4">
-        <f>(1+(F45-E45))-I45</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="I45" s="4">
         <f>48+22+14</f>
         <v>84</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>9</v>
@@ -3775,14 +3765,14 @@
         <v>15</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A46" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B46" s="23" t="s">
+      <c r="A46" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="4">
@@ -3798,18 +3788,18 @@
         <v>1974</v>
       </c>
       <c r="G46" s="4">
-        <f>(1+(F46-E46))-I46</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I46" s="4">
         <f>148</f>
         <v>148</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>9</v>
@@ -3818,14 +3808,14 @@
         <v>15</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A47" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B47" s="23" t="s">
+      <c r="A47" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="4">
@@ -3841,7 +3831,7 @@
         <v>1873</v>
       </c>
       <c r="G47" s="4">
-        <f>(1+(F47-E47))-I47</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="H47" s="3" t="s">
@@ -3851,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>9</v>
@@ -3860,14 +3850,14 @@
         <v>15</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A48" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" s="23" t="s">
+      <c r="A48" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="4">
@@ -3883,7 +3873,7 @@
         <v>1909</v>
       </c>
       <c r="G48" s="4">
-        <f>(1+(F48-E48))-I48</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="H48" s="3" t="s">
@@ -3893,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>9</v>
@@ -3902,12 +3892,12 @@
         <v>15</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>382</v>
+        <v>325</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -3925,7 +3915,7 @@
         <v>1851</v>
       </c>
       <c r="G49" s="4">
-        <f>(1+(F49-E49))-I49</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H49" s="3" t="s">
@@ -3935,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>9</v>
@@ -3943,13 +3933,13 @@
       <c r="L49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M49" s="11" t="s">
-        <v>355</v>
+      <c r="M49" s="6" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
-        <v>383</v>
+      <c r="A50" s="11" t="s">
+        <v>326</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -3967,17 +3957,17 @@
         <v>1988</v>
       </c>
       <c r="G50" s="4">
-        <f>(1+(F50-E50))-I50</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I50" s="4">
         <v>4</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>91</v>
@@ -3985,13 +3975,13 @@
       <c r="L50" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M50" s="11" t="s">
-        <v>355</v>
+      <c r="M50" s="6" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A51" s="12" t="s">
-        <v>383</v>
+      <c r="A51" s="11" t="s">
+        <v>326</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -4009,17 +3999,17 @@
         <v>1988</v>
       </c>
       <c r="G51" s="4">
-        <f>(1+(F51-E51))-I51</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I51" s="4">
         <v>4</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>9</v>
@@ -4027,13 +4017,13 @@
       <c r="L51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M51" s="11" t="s">
-        <v>355</v>
+      <c r="M51" s="6" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -4051,31 +4041,31 @@
         <v>1925</v>
       </c>
       <c r="G52" s="4">
-        <f>(1+(F52-E52))-I52</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="I52" s="4">
         <v>42</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -4093,31 +4083,31 @@
         <v>1964</v>
       </c>
       <c r="G53" s="4">
-        <f>(1+(F53-E53))-I53</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="I53" s="4">
         <v>10</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K53" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="M53" s="6" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -4135,7 +4125,7 @@
         <v>1982</v>
       </c>
       <c r="G54" s="4">
-        <f>(1+(F54-E54))-I54</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H54" s="3" t="s">
@@ -4145,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>9</v>
@@ -4153,13 +4143,13 @@
       <c r="L54" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M54" s="5" t="s">
-        <v>362</v>
+      <c r="M54" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -4177,18 +4167,18 @@
         <v>1836</v>
       </c>
       <c r="G55" s="4">
-        <f>(1+(F55-E55))-I55</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="I55" s="4">
         <f>98+33</f>
         <v>131</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>9</v>
@@ -4196,13 +4186,13 @@
       <c r="L55" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M55" s="5" t="s">
-        <v>366</v>
+      <c r="M55" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -4220,31 +4210,31 @@
         <v>1944</v>
       </c>
       <c r="G56" s="4">
-        <f>(1+(F56-E56))-I56</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="I56" s="4">
         <v>56</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M56" s="5" t="s">
-        <v>366</v>
+        <v>148</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -4262,7 +4252,7 @@
         <v>1836</v>
       </c>
       <c r="G57" s="4">
-        <f>(1+(F57-E57))-I57</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H57" s="3" t="s">
@@ -4272,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>9</v>
@@ -4280,13 +4270,13 @@
       <c r="L57" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M57" s="5" t="s">
-        <v>366</v>
+      <c r="M57" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -4304,32 +4294,32 @@
         <v>1943</v>
       </c>
       <c r="G58" s="4">
-        <f>(1+(F58-E58))-I58</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="I58" s="4">
         <f>31+20+6</f>
         <v>57</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M58" s="5" t="s">
-        <v>366</v>
+        <v>148</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -4347,17 +4337,17 @@
         <v>1855</v>
       </c>
       <c r="G59" s="4">
-        <f>(1+(F59-E59))-I59</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="I59" s="4">
         <v>19</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>9</v>
@@ -4365,13 +4355,13 @@
       <c r="L59" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M59" s="5" t="s">
-        <v>366</v>
+      <c r="M59" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -4389,32 +4379,32 @@
         <v>1944</v>
       </c>
       <c r="G60" s="4">
-        <f>(1+(F60-E60))-I60</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="I60" s="4">
         <f>1+30+1+18+4+4</f>
         <v>58</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M60" s="5" t="s">
-        <v>366</v>
+        <v>148</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -4432,32 +4422,32 @@
         <v>2004</v>
       </c>
       <c r="G61" s="4">
-        <f>(1+(F61-E61))-I61</f>
+        <f t="shared" si="1"/>
         <v>54.5</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="I61" s="4">
         <f>6+0.5+2</f>
         <v>8.5</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>43</v>
@@ -4475,7 +4465,7 @@
         <v>1920</v>
       </c>
       <c r="G62" s="4">
-        <f>(1+(F62-E62))-I62</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="H62" s="3" t="s">
@@ -4485,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>9</v>
@@ -4494,12 +4484,12 @@
         <v>15</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>83</v>
@@ -4517,7 +4507,7 @@
         <v>1972</v>
       </c>
       <c r="G63" s="4">
-        <f>(1+(F63-E63))-I63</f>
+        <f t="shared" si="1"/>
         <v>1.2634446691001457</v>
       </c>
       <c r="H63" s="3" t="s">
@@ -4528,7 +4518,7 @@
         <v>9.7365553308998543</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>9</v>
@@ -4536,16 +4526,16 @@
       <c r="L63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M63" s="5" t="s">
-        <v>338</v>
+      <c r="M63" s="6" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="21" t="s">
         <v>128</v>
-      </c>
-      <c r="B64" s="23" t="s">
-        <v>129</v>
       </c>
       <c r="C64" s="4">
         <v>53.890380999999998</v>
@@ -4560,7 +4550,7 @@
         <v>1995</v>
       </c>
       <c r="G64" s="4">
-        <f>(1+(F64-E64))-I64</f>
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="H64" s="3" t="s">
@@ -4570,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>9</v>
@@ -4579,15 +4569,15 @@
         <v>15</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>352</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="21" t="s">
         <v>128</v>
-      </c>
-      <c r="B65" s="23" t="s">
-        <v>129</v>
       </c>
       <c r="C65" s="4">
         <v>53.890380999999998</v>
@@ -4602,7 +4592,7 @@
         <v>1898</v>
       </c>
       <c r="G65" s="4">
-        <f>(1+(F65-E65))-I65</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="H65" s="3" t="s">
@@ -4612,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>9</v>
@@ -4621,7 +4611,7 @@
         <v>15</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>352</v>
+        <v>416</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
@@ -4644,7 +4634,7 @@
         <v>1968</v>
       </c>
       <c r="G66" s="4">
-        <f>(1+(F66-E66))-I66</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="H66" s="3" t="s">
@@ -4654,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>9</v>
@@ -4663,7 +4653,7 @@
         <v>15</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
@@ -4686,7 +4676,7 @@
         <v>1968</v>
       </c>
       <c r="G67" s="4">
-        <f>(1+(F67-E67))-I67</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="H67" s="3" t="s">
@@ -4696,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>9</v>
@@ -4705,7 +4695,7 @@
         <v>15</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
@@ -4728,7 +4718,7 @@
         <v>1979</v>
       </c>
       <c r="G68" s="4">
-        <f>(1+(F68-E68))-I68</f>
+        <f t="shared" si="1"/>
         <v>1.8333333333333428</v>
       </c>
       <c r="H68" s="3" t="s">
@@ -4739,7 +4729,7 @@
         <v>136.16666666666666</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>9</v>
@@ -4748,7 +4738,7 @@
         <v>15</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4771,7 +4761,7 @@
         <v>1980</v>
       </c>
       <c r="G69" s="4">
-        <f>(1+(F69-E69))-I69</f>
+        <f t="shared" si="1"/>
         <v>1.863636363636374</v>
       </c>
       <c r="H69" s="3" t="s">
@@ -4782,7 +4772,7 @@
         <v>137.13636363636363</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>9</v>
@@ -4791,7 +4781,7 @@
         <v>15</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4814,7 +4804,7 @@
         <v>1978</v>
       </c>
       <c r="G70" s="4">
-        <f>(1+(F70-E70))-I70</f>
+        <f t="shared" si="1"/>
         <v>1.3333333333333428</v>
       </c>
       <c r="H70" s="3" t="s">
@@ -4825,7 +4815,7 @@
         <v>135.66666666666666</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>9</v>
@@ -4834,12 +4824,12 @@
         <v>15</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>385</v>
+        <v>328</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>13</v>
@@ -4857,7 +4847,7 @@
         <v>1842</v>
       </c>
       <c r="G71" s="4">
-        <f>(1+(F71-E71))-I71</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
       <c r="H71" s="3" t="s">
@@ -4867,7 +4857,7 @@
         <v>0.75</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>9</v>
@@ -4876,12 +4866,12 @@
         <v>15</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>13</v>
@@ -4899,7 +4889,7 @@
         <v>1906</v>
       </c>
       <c r="G72" s="4">
-        <f>(1+(F72-E72))-I72</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H72" s="3" t="s">
@@ -4909,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>9</v>
@@ -4918,12 +4908,12 @@
         <v>15</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="16" t="s">
-        <v>247</v>
+      <c r="A73" s="14" t="s">
+        <v>246</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>13</v>
@@ -4941,7 +4931,7 @@
         <v>1931</v>
       </c>
       <c r="G73" s="4">
-        <f>(1+(F73-E73))-I73</f>
+        <f t="shared" si="1"/>
         <v>4.3531827515400412</v>
       </c>
       <c r="H73" s="8" t="s">
@@ -4952,23 +4942,23 @@
         <v>2.6468172484599588</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M73" s="5" t="s">
-        <v>375</v>
+      <c r="M73" s="6" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="12" t="s">
         <v>87</v>
       </c>
       <c r="C74" s="7">
@@ -4993,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>91</v>
@@ -5002,14 +4992,14 @@
         <v>15</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>341</v>
+        <v>381</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="12" t="s">
         <v>87</v>
       </c>
       <c r="C75" s="7">
@@ -5034,7 +5024,7 @@
         <v>4.8</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>91</v>
@@ -5043,14 +5033,14 @@
         <v>15</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>341</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="12" t="s">
         <v>87</v>
       </c>
       <c r="C76" s="7">
@@ -5075,7 +5065,7 @@
         <v>1.48</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>91</v>
@@ -5084,14 +5074,14 @@
         <v>15</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>341</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="12" t="s">
         <v>87</v>
       </c>
       <c r="C77" s="7">
@@ -5116,7 +5106,7 @@
         <v>1.51</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>91</v>
@@ -5125,12 +5115,12 @@
         <v>15</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>341</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="13" t="s">
-        <v>386</v>
+      <c r="A78" s="12" t="s">
+        <v>329</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>87</v>
@@ -5148,17 +5138,17 @@
         <v>1934</v>
       </c>
       <c r="G78" s="4">
-        <f>(1+(F78-E78))-I78</f>
+        <f t="shared" ref="G78:G89" si="2">(1+(F78-E78))-I78</f>
         <v>50</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="I78" s="9">
         <v>12</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>9</v>
@@ -5166,13 +5156,13 @@
       <c r="L78" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M78" s="5" t="s">
-        <v>363</v>
+      <c r="M78" s="6" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="13" t="s">
-        <v>387</v>
+      <c r="A79" s="12" t="s">
+        <v>330</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>87</v>
@@ -5190,17 +5180,17 @@
         <v>1957</v>
       </c>
       <c r="G79" s="4">
-        <f>(1+(F79-E79))-I79</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="I79" s="9">
         <v>3</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K79" s="8" t="s">
         <v>21</v>
@@ -5208,13 +5198,13 @@
       <c r="L79" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M79" s="5" t="s">
-        <v>363</v>
+      <c r="M79" s="6" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="13" t="s">
-        <v>388</v>
+      <c r="A80" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>87</v>
@@ -5232,7 +5222,7 @@
         <v>1986</v>
       </c>
       <c r="G80" s="4">
-        <f>(1+(F80-E80))-I80</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="H80" s="8" t="s">
@@ -5242,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K80" s="8" t="s">
         <v>21</v>
@@ -5250,16 +5240,16 @@
       <c r="L80" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M80" s="5" t="s">
-        <v>363</v>
+      <c r="M80" s="6" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="29" t="s">
+      <c r="A81" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="C81" s="4">
         <v>5.3038499999999997</v>
@@ -5274,7 +5264,7 @@
         <v>2011</v>
       </c>
       <c r="G81" s="4">
-        <f>(1+(F81-E81))-I81</f>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="H81" s="3" t="s">
@@ -5284,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>91</v>
@@ -5293,7 +5283,7 @@
         <v>15</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5316,7 +5306,7 @@
         <v>1968</v>
       </c>
       <c r="G82" s="4">
-        <f>(1+(F82-E82))-I82</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="H82" s="3" t="s">
@@ -5326,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>9</v>
@@ -5335,15 +5325,15 @@
         <v>15</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="23" t="s">
+      <c r="A83" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B83" s="21" t="s">
         <v>137</v>
-      </c>
-      <c r="B83" s="23" t="s">
-        <v>138</v>
       </c>
       <c r="C83" s="7">
         <v>38.296666999999999</v>
@@ -5358,7 +5348,7 @@
         <v>2013</v>
       </c>
       <c r="G83" s="4">
-        <f>(1+(F83-E83))-I83</f>
+        <f t="shared" si="2"/>
         <v>52</v>
       </c>
       <c r="H83" s="3" t="s">
@@ -5368,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K83" s="8" t="s">
         <v>21</v>
@@ -5376,16 +5366,16 @@
       <c r="L83" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M83" s="5" t="s">
-        <v>353</v>
+      <c r="M83" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B84" s="23" t="s">
+      <c r="A84" s="21" t="s">
         <v>138</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>137</v>
       </c>
       <c r="C84" s="4">
         <v>35.646303000000003</v>
@@ -5400,7 +5390,7 @@
         <v>2013</v>
       </c>
       <c r="G84" s="4">
-        <f>(1+(F84-E84))-I84</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="H84" s="3" t="s">
@@ -5410,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K84" s="8" t="s">
         <v>21</v>
@@ -5418,16 +5408,16 @@
       <c r="L84" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M84" s="5" t="s">
-        <v>353</v>
+      <c r="M84" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B85" s="23" t="s">
-        <v>138</v>
+      <c r="A85" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>137</v>
       </c>
       <c r="C85" s="4">
         <v>35.456859000000001</v>
@@ -5442,7 +5432,7 @@
         <v>2013</v>
       </c>
       <c r="G85" s="4">
-        <f>(1+(F85-E85))-I85</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="H85" s="3" t="s">
@@ -5452,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K85" s="8" t="s">
         <v>21</v>
@@ -5460,8 +5450,8 @@
       <c r="L85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M85" s="5" t="s">
-        <v>353</v>
+      <c r="M85" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5484,7 +5474,7 @@
         <v>1893</v>
       </c>
       <c r="G86" s="4">
-        <f>(1+(F86-E86))-I86</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H86" s="3" t="s">
@@ -5494,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>9</v>
@@ -5503,14 +5493,14 @@
         <v>15</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>336</v>
+        <v>379</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B87" s="23" t="s">
+      <c r="A87" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C87" s="4">
@@ -5526,7 +5516,7 @@
         <v>2013</v>
       </c>
       <c r="G87" s="4">
-        <f>(1+(F87-E87))-I87</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="H87" s="3" t="s">
@@ -5544,15 +5534,15 @@
       <c r="L87" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M87" s="5" t="s">
-        <v>353</v>
+      <c r="M87" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B88" s="23" t="s">
+      <c r="A88" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B88" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C88" s="4">
@@ -5568,7 +5558,7 @@
         <v>2013</v>
       </c>
       <c r="G88" s="4">
-        <f>(1+(F88-E88))-I88</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H88" s="3" t="s">
@@ -5586,8 +5576,8 @@
       <c r="L88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M88" s="5" t="s">
-        <v>353</v>
+      <c r="M88" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.35">
@@ -5610,7 +5600,7 @@
         <v>1967</v>
       </c>
       <c r="G89" s="4">
-        <f>(1+(F89-E89))-I89</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H89" s="3" t="s">
@@ -5620,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>9</v>
@@ -5629,40 +5619,40 @@
         <v>15</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A90" s="18" t="s">
-        <v>324</v>
+      <c r="A90" s="16" t="s">
+        <v>311</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C90" s="19">
+        <v>146</v>
+      </c>
+      <c r="C90" s="17">
         <v>79.919178000000002</v>
       </c>
-      <c r="D90" s="19">
+      <c r="D90" s="17">
         <v>16.832923999999998</v>
       </c>
-      <c r="E90" s="17">
+      <c r="E90" s="15">
         <v>1900</v>
       </c>
-      <c r="F90" s="17">
+      <c r="F90" s="15">
         <v>1900</v>
       </c>
       <c r="G90" s="4">
         <f>1-I90</f>
         <v>0.29000000000000004</v>
       </c>
-      <c r="H90" s="17" t="s">
-        <v>325</v>
+      <c r="H90" s="15" t="s">
+        <v>312</v>
       </c>
       <c r="I90" s="4">
         <v>0.71</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>9</v>
@@ -5670,83 +5660,83 @@
       <c r="L90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M90" s="5" t="s">
-        <v>377</v>
+      <c r="M90" s="6" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A91" s="18" t="s">
-        <v>270</v>
+      <c r="A91" s="16" t="s">
+        <v>257</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C91" s="19">
+        <v>146</v>
+      </c>
+      <c r="C91" s="17">
         <v>79.875488000000004</v>
       </c>
-      <c r="D91" s="19">
+      <c r="D91" s="17">
         <v>16.062946</v>
       </c>
-      <c r="E91" s="17">
+      <c r="E91" s="15">
         <v>1872</v>
       </c>
-      <c r="F91" s="17">
+      <c r="F91" s="15">
         <v>1873</v>
       </c>
       <c r="G91" s="4">
         <f>2-I91</f>
         <v>0.29000000000000004</v>
       </c>
-      <c r="H91" s="17" t="s">
-        <v>326</v>
+      <c r="H91" s="15" t="s">
+        <v>313</v>
       </c>
       <c r="I91" s="4">
         <v>1.71</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="M91" s="5" t="s">
-        <v>377</v>
+        <v>314</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A92" s="18" t="s">
-        <v>328</v>
+      <c r="A92" s="16" t="s">
+        <v>315</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C92" s="19">
+        <v>146</v>
+      </c>
+      <c r="C92" s="17">
         <v>79.718778</v>
       </c>
-      <c r="D92" s="19">
+      <c r="D92" s="17">
         <v>10.965166</v>
       </c>
-      <c r="E92" s="17">
+      <c r="E92" s="15">
         <v>1897</v>
       </c>
-      <c r="F92" s="17">
+      <c r="F92" s="15">
         <v>1897</v>
       </c>
       <c r="G92" s="4">
         <f>1-I92</f>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="H92" s="17" t="s">
-        <v>329</v>
+      <c r="H92" s="15" t="s">
+        <v>316</v>
       </c>
       <c r="I92" s="4">
         <v>0.9</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>9</v>
@@ -5754,8 +5744,8 @@
       <c r="L92" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M92" s="5" t="s">
-        <v>377</v>
+      <c r="M92" s="6" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.35">
@@ -5778,7 +5768,7 @@
         <v>1998</v>
       </c>
       <c r="G93" s="4">
-        <f>(1+(F93-E93))-I93</f>
+        <f t="shared" ref="G93:G124" si="3">(1+(F93-E93))-I93</f>
         <v>16</v>
       </c>
       <c r="H93" s="3" t="s">
@@ -5788,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K93" s="3" t="s">
         <v>9</v>
@@ -5797,7 +5787,7 @@
         <v>15</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.35">
@@ -5820,7 +5810,7 @@
         <v>1974</v>
       </c>
       <c r="G94" s="4">
-        <f>(1+(F94-E94))-I94</f>
+        <f t="shared" si="3"/>
         <v>68</v>
       </c>
       <c r="H94" s="3" t="s">
@@ -5830,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>9</v>
@@ -5839,14 +5829,14 @@
         <v>15</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A95" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B95" s="23" t="s">
+      <c r="A95" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B95" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C95" s="4">
@@ -5862,7 +5852,7 @@
         <v>2013</v>
       </c>
       <c r="G95" s="4">
-        <f>(1+(F95-E95))-I95</f>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="H95" s="3" t="s">
@@ -5872,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K95" s="8" t="s">
         <v>21</v>
@@ -5880,15 +5870,15 @@
       <c r="L95" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M95" s="5" t="s">
-        <v>353</v>
+      <c r="M95" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A96" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="B96" s="23" t="s">
+      <c r="A96" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="B96" s="21" t="s">
         <v>119</v>
       </c>
       <c r="C96" s="4">
@@ -5904,7 +5894,7 @@
         <v>2004</v>
       </c>
       <c r="G96" s="4">
-        <f>(1+(F96-E96))-I96</f>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="H96" s="3" t="s">
@@ -5914,24 +5904,24 @@
         <v>34</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M96" s="11" t="s">
-        <v>121</v>
+      <c r="M96" s="6" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C97" s="4">
         <v>1.2865660000000001</v>
@@ -5946,17 +5936,17 @@
         <v>1841</v>
       </c>
       <c r="G97" s="4">
-        <f>(1+(F97-E97))-I97</f>
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="I97" s="4">
         <v>6.5</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>21</v>
@@ -5964,16 +5954,16 @@
       <c r="L97" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M97" s="24" t="s">
-        <v>330</v>
+      <c r="M97" s="22" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C98" s="7">
         <v>1.2669999999999999</v>
@@ -5988,7 +5978,7 @@
         <v>1865</v>
       </c>
       <c r="G98" s="4">
-        <f>(1+(F98-E98))-I98</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H98" s="8" t="s">
@@ -5998,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>21</v>
@@ -6006,16 +5996,16 @@
       <c r="L98" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M98" s="24" t="s">
-        <v>330</v>
+      <c r="M98" s="22" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C99" s="7">
         <v>1.4670000000000001</v>
@@ -6030,11 +6020,11 @@
         <v>1947</v>
       </c>
       <c r="G99" s="4">
-        <f>(1+(F99-E99))-I99</f>
+        <f t="shared" si="3"/>
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="I99" s="4">
         <v>0.91</v>
@@ -6048,8 +6038,8 @@
       <c r="L99" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M99" s="24" t="s">
-        <v>330</v>
+      <c r="M99" s="22" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
@@ -6072,7 +6062,7 @@
         <v>1924</v>
       </c>
       <c r="G100" s="4">
-        <f>(1+(F100-E100))-I100</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="H100" s="3" t="s">
@@ -6082,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>9</v>
@@ -6090,8 +6080,8 @@
       <c r="L100" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="M100" s="5" t="s">
-        <v>347</v>
+      <c r="M100" s="6" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
@@ -6114,7 +6104,7 @@
         <v>1956</v>
       </c>
       <c r="G101" s="4">
-        <f>(1+(F101-E101))-I101</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H101" s="3" t="s">
@@ -6124,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>9</v>
@@ -6132,8 +6122,8 @@
       <c r="L101" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M101" s="5" t="s">
-        <v>350</v>
+      <c r="M101" s="6" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
@@ -6156,7 +6146,7 @@
         <v>1990</v>
       </c>
       <c r="G102" s="4">
-        <f>(1+(F102-E102))-I102</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="H102" s="3">
@@ -6166,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>9</v>
@@ -6174,8 +6164,8 @@
       <c r="L102" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M102" s="5" t="s">
-        <v>350</v>
+      <c r="M102" s="6" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.35">
@@ -6198,7 +6188,7 @@
         <v>1957</v>
       </c>
       <c r="G103" s="4">
-        <f>(1+(F103-E103))-I103</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H103" s="3" t="s">
@@ -6208,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>9</v>
@@ -6216,13 +6206,13 @@
       <c r="L103" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M103" s="5" t="s">
-        <v>350</v>
+      <c r="M103" s="6" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>108</v>
@@ -6240,7 +6230,7 @@
         <v>1874</v>
       </c>
       <c r="G104" s="4">
-        <f>(1+(F104-E104))-I104</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="H104" s="3" t="s">
@@ -6250,21 +6240,21 @@
         <v>0</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="M104" s="5" t="s">
-        <v>367</v>
+        <v>220</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>390</v>
+        <v>333</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>108</v>
@@ -6282,32 +6272,32 @@
         <v>1924</v>
       </c>
       <c r="G105" s="4">
-        <f>(1+(F105-E105))-I105</f>
+        <f t="shared" si="3"/>
         <v>47.917864476386036</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I105" s="4">
         <f>3+(30/365.25)</f>
         <v>3.0821355236139629</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="M105" s="5" t="s">
-        <v>367</v>
+        <v>221</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>391</v>
+        <v>334</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>108</v>
@@ -6325,18 +6315,18 @@
         <v>1989</v>
       </c>
       <c r="G106" s="4">
-        <f>(1+(F106-E106))-I106</f>
+        <f t="shared" si="3"/>
         <v>51.915126625598901</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="I106" s="4">
         <f>3+((31+30+31+30)/365.25)+4-((30+31+30)/365.25)+4</f>
         <v>11.084873374401095</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>9</v>
@@ -6344,13 +6334,13 @@
       <c r="L106" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M106" s="5" t="s">
-        <v>367</v>
+      <c r="M106" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A107" s="13" t="s">
-        <v>392</v>
+      <c r="A107" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>108</v>
@@ -6368,7 +6358,7 @@
         <v>1971</v>
       </c>
       <c r="G107" s="4">
-        <f>(1+(F107-E107))-I107</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H107" s="3" t="s">
@@ -6378,21 +6368,21 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="M107" s="5" t="s">
-        <v>367</v>
+        <v>222</v>
+      </c>
+      <c r="M107" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>108</v>
@@ -6410,7 +6400,7 @@
         <v>1996</v>
       </c>
       <c r="G108" s="4">
-        <f>(1+(F108-E108))-I108</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="H108" s="3" t="s">
@@ -6420,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>9</v>
@@ -6428,13 +6418,13 @@
       <c r="L108" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M108" s="5" t="s">
-        <v>367</v>
+      <c r="M108" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
-        <v>393</v>
+        <v>336</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>108</v>
@@ -6452,31 +6442,31 @@
         <v>1924</v>
       </c>
       <c r="G109" s="4">
-        <f>(1+(F109-E109))-I109</f>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="I109" s="4">
         <v>5</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="M109" s="5" t="s">
-        <v>367</v>
+        <v>221</v>
+      </c>
+      <c r="M109" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>394</v>
+        <v>337</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>108</v>
@@ -6494,7 +6484,7 @@
         <v>1925</v>
       </c>
       <c r="G110" s="4">
-        <f>(1+(F110-E110))-I110</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="H110" s="3" t="s">
@@ -6504,21 +6494,21 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="M110" s="5" t="s">
-        <v>367</v>
+        <v>221</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>395</v>
+        <v>338</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>108</v>
@@ -6536,7 +6526,7 @@
         <v>1928</v>
       </c>
       <c r="G111" s="4">
-        <f>(1+(F111-E111))-I111</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H111" s="3" t="s">
@@ -6546,16 +6536,16 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="M111" s="5" t="s">
-        <v>367</v>
+        <v>221</v>
+      </c>
+      <c r="M111" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
@@ -6578,7 +6568,7 @@
         <v>1996</v>
       </c>
       <c r="G112" s="4">
-        <f>(1+(F112-E112))-I112</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="H112" s="3" t="s">
@@ -6588,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>9</v>
@@ -6597,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.35">
@@ -6620,7 +6610,7 @@
         <v>1992</v>
       </c>
       <c r="G113" s="4">
-        <f>(1+(F113-E113))-I113</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="H113" s="3" t="s">
@@ -6630,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>9</v>
@@ -6639,7 +6629,7 @@
         <v>15</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.35">
@@ -6662,7 +6652,7 @@
         <v>1989</v>
       </c>
       <c r="G114" s="4">
-        <f>(1+(F114-E114))-I114</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H114" s="3" t="s">
@@ -6672,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>9</v>
@@ -6680,8 +6670,8 @@
       <c r="L114" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M114" s="5" t="s">
-        <v>343</v>
+      <c r="M114" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.35">
@@ -6704,7 +6694,7 @@
         <v>1990</v>
       </c>
       <c r="G115" s="4">
-        <f>(1+(F115-E115))-I115</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H115" s="3">
@@ -6714,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>9</v>
@@ -6722,8 +6712,8 @@
       <c r="L115" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M115" s="5" t="s">
-        <v>343</v>
+      <c r="M115" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.35">
@@ -6746,7 +6736,7 @@
         <v>2006</v>
       </c>
       <c r="G116" s="4">
-        <f>(1+(F116-E116))-I116</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="H116" s="3" t="s">
@@ -6756,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K116" s="3" t="s">
         <v>9</v>
@@ -6764,8 +6754,8 @@
       <c r="L116" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M116" s="5" t="s">
-        <v>343</v>
+      <c r="M116" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.35">
@@ -6788,7 +6778,7 @@
         <v>1989</v>
       </c>
       <c r="G117" s="4">
-        <f>(1+(F117-E117))-I117</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="H117" s="3" t="s">
@@ -6799,7 +6789,7 @@
         <v>18</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K117" s="3" t="s">
         <v>9</v>
@@ -6807,8 +6797,8 @@
       <c r="L117" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M117" s="5" t="s">
-        <v>343</v>
+      <c r="M117" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.35">
@@ -6831,7 +6821,7 @@
         <v>1990</v>
       </c>
       <c r="G118" s="4">
-        <f>(1+(F118-E118))-I118</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H118" s="3" t="s">
@@ -6841,7 +6831,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K118" s="3" t="s">
         <v>9</v>
@@ -6849,13 +6839,13 @@
       <c r="L118" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M118" s="5" t="s">
-        <v>343</v>
+      <c r="M118" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>23</v>
@@ -6873,7 +6863,7 @@
         <v>1957</v>
       </c>
       <c r="G119" s="4">
-        <f>(1+(F119-E119))-I119</f>
+        <f t="shared" si="3"/>
         <v>57</v>
       </c>
       <c r="H119" s="3" t="s">
@@ -6883,21 +6873,21 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M119" s="5" t="s">
-        <v>356</v>
+        <v>148</v>
+      </c>
+      <c r="M119" s="6" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>23</v>
@@ -6915,7 +6905,7 @@
         <v>1972</v>
       </c>
       <c r="G120" s="4">
-        <f>(1+(F120-E120))-I120</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="H120" s="3" t="s">
@@ -6925,21 +6915,21 @@
         <v>0</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M120" s="5" t="s">
-        <v>356</v>
+        <v>148</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
-        <v>398</v>
+        <v>341</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>23</v>
@@ -6957,7 +6947,7 @@
         <v>1986</v>
       </c>
       <c r="G121" s="4">
-        <f>(1+(F121-E121))-I121</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="H121" s="3" t="s">
@@ -6967,21 +6957,21 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M121" s="5" t="s">
-        <v>356</v>
+        <v>148</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
-        <v>399</v>
+        <v>342</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>23</v>
@@ -6999,7 +6989,7 @@
         <v>2001</v>
       </c>
       <c r="G122" s="4">
-        <f>(1+(F122-E122))-I122</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="H122" s="3" t="s">
@@ -7009,21 +6999,21 @@
         <v>0</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="L122" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M122" s="5" t="s">
-        <v>356</v>
+      <c r="M122" s="6" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>23</v>
@@ -7041,31 +7031,31 @@
         <v>1979</v>
       </c>
       <c r="G123" s="4">
-        <f>(1+(F123-E123))-I123</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="I123" s="4">
         <v>49</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="M123" s="5" t="s">
-        <v>368</v>
+        <v>225</v>
+      </c>
+      <c r="M123" s="6" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>23</v>
@@ -7083,7 +7073,7 @@
         <v>1995</v>
       </c>
       <c r="G124" s="4">
-        <f>(1+(F124-E124))-I124</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="H124" s="3">
@@ -7093,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K124" s="3" t="s">
         <v>9</v>
@@ -7101,13 +7091,13 @@
       <c r="L124" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M124" s="5" t="s">
-        <v>371</v>
+      <c r="M124" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>23</v>
@@ -7125,7 +7115,7 @@
         <v>1995</v>
       </c>
       <c r="G125" s="4">
-        <f>(1+(F125-E125))-I125</f>
+        <f t="shared" ref="G125:G156" si="4">(1+(F125-E125))-I125</f>
         <v>28</v>
       </c>
       <c r="H125" s="3">
@@ -7135,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K125" s="3" t="s">
         <v>9</v>
@@ -7143,13 +7133,13 @@
       <c r="L125" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M125" s="5" t="s">
-        <v>371</v>
+      <c r="M125" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>23</v>
@@ -7167,7 +7157,7 @@
         <v>1974</v>
       </c>
       <c r="G126" s="4">
-        <f>(1+(F126-E126))-I126</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H126" s="3" t="s">
@@ -7177,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>9</v>
@@ -7185,13 +7175,13 @@
       <c r="L126" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M126" s="5" t="s">
-        <v>371</v>
+      <c r="M126" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>23</v>
@@ -7209,7 +7199,7 @@
         <v>1995</v>
       </c>
       <c r="G127" s="4">
-        <f>(1+(F127-E127))-I127</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="H127" s="3" t="s">
@@ -7219,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>9</v>
@@ -7227,13 +7217,13 @@
       <c r="L127" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M127" s="5" t="s">
-        <v>371</v>
+      <c r="M127" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>23</v>
@@ -7251,7 +7241,7 @@
         <v>1983</v>
       </c>
       <c r="G128" s="4">
-        <f>(1+(F128-E128))-I128</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="H128" s="3" t="s">
@@ -7261,7 +7251,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K128" s="3" t="s">
         <v>9</v>
@@ -7269,13 +7259,13 @@
       <c r="L128" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M128" s="5" t="s">
-        <v>371</v>
+      <c r="M128" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>23</v>
@@ -7293,7 +7283,7 @@
         <v>1995</v>
       </c>
       <c r="G129" s="4">
-        <f>(1+(F129-E129))-I129</f>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="H129" s="3" t="s">
@@ -7303,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>9</v>
@@ -7311,13 +7301,13 @@
       <c r="L129" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M129" s="5" t="s">
-        <v>371</v>
+      <c r="M129" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>23</v>
@@ -7335,17 +7325,17 @@
         <v>1990</v>
       </c>
       <c r="G130" s="4">
-        <f>(1+(F130-E130))-I130</f>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="I130" s="4">
         <v>40</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K130" s="3" t="s">
         <v>9</v>
@@ -7353,13 +7343,13 @@
       <c r="L130" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M130" s="5" t="s">
-        <v>371</v>
+      <c r="M130" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>400</v>
+        <v>343</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>23</v>
@@ -7377,7 +7367,7 @@
         <v>1975</v>
       </c>
       <c r="G131" s="4">
-        <f>(1+(F131-E131))-I131</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="H131" s="3" t="s">
@@ -7387,7 +7377,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K131" s="3" t="s">
         <v>9</v>
@@ -7395,13 +7385,13 @@
       <c r="L131" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M131" s="5" t="s">
-        <v>371</v>
+      <c r="M131" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>23</v>
@@ -7419,7 +7409,7 @@
         <v>1934</v>
       </c>
       <c r="G132" s="4">
-        <f>(1+(F132-E132))-I132</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="H132" s="3" t="s">
@@ -7429,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K132" s="3" t="s">
         <v>9</v>
@@ -7437,13 +7427,13 @@
       <c r="L132" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M132" s="5" t="s">
-        <v>371</v>
+      <c r="M132" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>23</v>
@@ -7461,7 +7451,7 @@
         <v>1995</v>
       </c>
       <c r="G133" s="4">
-        <f>(1+(F133-E133))-I133</f>
+        <f t="shared" si="4"/>
         <v>67</v>
       </c>
       <c r="H133" s="3" t="s">
@@ -7471,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K133" s="3" t="s">
         <v>9</v>
@@ -7479,13 +7469,13 @@
       <c r="L133" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M133" s="5" t="s">
-        <v>371</v>
+      <c r="M133" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>23</v>
@@ -7503,7 +7493,7 @@
         <v>1929</v>
       </c>
       <c r="G134" s="4">
-        <f>(1+(F134-E134))-I134</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="H134" s="3" t="s">
@@ -7513,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K134" s="3" t="s">
         <v>9</v>
@@ -7521,13 +7511,13 @@
       <c r="L134" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M134" s="5" t="s">
-        <v>371</v>
+      <c r="M134" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>23</v>
@@ -7545,7 +7535,7 @@
         <v>1911</v>
       </c>
       <c r="G135" s="4">
-        <f>(1+(F135-E135))-I135</f>
+        <f t="shared" si="4"/>
         <v>8.333333333333337E-2</v>
       </c>
       <c r="H135" s="3" t="s">
@@ -7556,7 +7546,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K135" s="3" t="s">
         <v>9</v>
@@ -7564,13 +7554,13 @@
       <c r="L135" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M135" s="5" t="s">
-        <v>371</v>
+      <c r="M135" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>23</v>
@@ -7588,7 +7578,7 @@
         <v>1918</v>
       </c>
       <c r="G136" s="4">
-        <f>(1+(F136-E136))-I136</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="H136" s="3" t="s">
@@ -7598,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K136" s="3" t="s">
         <v>9</v>
@@ -7606,13 +7596,13 @@
       <c r="L136" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M136" s="5" t="s">
-        <v>371</v>
+      <c r="M136" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>23</v>
@@ -7630,7 +7620,7 @@
         <v>1924</v>
       </c>
       <c r="G137" s="4">
-        <f>(1+(F137-E137))-I137</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="H137" s="3" t="s">
@@ -7640,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K137" s="3" t="s">
         <v>9</v>
@@ -7648,13 +7638,13 @@
       <c r="L137" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M137" s="5" t="s">
-        <v>371</v>
+      <c r="M137" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>23</v>
@@ -7672,7 +7662,7 @@
         <v>1995</v>
       </c>
       <c r="G138" s="4">
-        <f>(1+(F138-E138))-I138</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="H138" s="3" t="s">
@@ -7682,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K138" s="3" t="s">
         <v>9</v>
@@ -7690,13 +7680,13 @@
       <c r="L138" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M138" s="5" t="s">
-        <v>371</v>
+      <c r="M138" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>23</v>
@@ -7714,7 +7704,7 @@
         <v>1904</v>
       </c>
       <c r="G139" s="4">
-        <f>(1+(F139-E139))-I139</f>
+        <f t="shared" si="4"/>
         <v>52</v>
       </c>
       <c r="H139" s="3" t="s">
@@ -7724,21 +7714,21 @@
         <v>0</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="M139" s="5" t="s">
-        <v>378</v>
+        <v>249</v>
+      </c>
+      <c r="M139" s="6" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>23</v>
@@ -7756,7 +7746,7 @@
         <v>1904</v>
       </c>
       <c r="G140" s="4">
-        <f>(1+(F140-E140))-I140</f>
+        <f t="shared" si="4"/>
         <v>52</v>
       </c>
       <c r="H140" s="3" t="s">
@@ -7766,16 +7756,16 @@
         <v>0</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="M140" s="5" t="s">
-        <v>378</v>
+        <v>249</v>
+      </c>
+      <c r="M140" s="6" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.35">
@@ -7798,7 +7788,7 @@
         <v>1923</v>
       </c>
       <c r="G141" s="4">
-        <f>(1+(F141-E141))-I141</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="H141" s="3" t="s">
@@ -7808,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K141" s="3" t="s">
         <v>9</v>
@@ -7817,7 +7807,7 @@
         <v>15</v>
       </c>
       <c r="M141" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.35">
@@ -7840,7 +7830,7 @@
         <v>1950</v>
       </c>
       <c r="G142" s="4">
-        <f>(1+(F142-E142))-I142</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="H142" s="3" t="s">
@@ -7850,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>9</v>
@@ -7859,7 +7849,7 @@
         <v>15</v>
       </c>
       <c r="M142" s="6" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.35">
@@ -7882,7 +7872,7 @@
         <v>1877</v>
       </c>
       <c r="G143" s="4">
-        <f>(1+(F143-E143))-I143</f>
+        <f t="shared" si="4"/>
         <v>23.5</v>
       </c>
       <c r="H143" s="3" t="s">
@@ -7901,7 +7891,7 @@
         <v>15</v>
       </c>
       <c r="M143" s="6" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.35">
@@ -7924,11 +7914,11 @@
         <v>2000</v>
       </c>
       <c r="G144" s="4">
-        <f>(1+(F144-E144))-I144</f>
+        <f t="shared" si="4"/>
         <v>103.5</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="I144" s="4">
         <v>0.5</v>
@@ -7942,11 +7932,11 @@
       <c r="L144" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M144" s="25" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M144" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>85</v>
       </c>
@@ -7966,7 +7956,7 @@
         <v>2000</v>
       </c>
       <c r="G145" s="4">
-        <f>(1+(F145-E145))-I145</f>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="H145" s="8" t="s">
@@ -7976,7 +7966,7 @@
         <v>13</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K145" s="8" t="s">
         <v>21</v>
@@ -7984,11 +7974,11 @@
       <c r="L145" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M145" s="31" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M145" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>86</v>
       </c>
@@ -8008,7 +7998,7 @@
         <v>2000</v>
       </c>
       <c r="G146" s="4">
-        <f>(1+(F146-E146))-I146</f>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="H146" s="3" t="s">
@@ -8018,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K146" s="8" t="s">
         <v>21</v>
@@ -8026,15 +8016,15 @@
       <c r="L146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M146" s="31" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A147" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B147" s="23" t="s">
+      <c r="M146" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A147" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B147" s="21" t="s">
         <v>20</v>
       </c>
       <c r="C147" s="4">
@@ -8050,11 +8040,11 @@
         <v>2013</v>
       </c>
       <c r="G147" s="4">
-        <f>(1+(F147-E147))-I147</f>
+        <f t="shared" si="4"/>
         <v>113</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="I147" s="4">
         <v>2</v>
@@ -8068,13 +8058,13 @@
       <c r="L147" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M147" s="31" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M147" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
-        <v>402</v>
+        <v>345</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>20</v>
@@ -8092,31 +8082,31 @@
         <v>1885</v>
       </c>
       <c r="G148" s="4">
-        <f>(1+(F148-E148))-I148</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="I148" s="4">
         <v>5</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="L148" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M148" s="31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M148" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
-        <v>402</v>
+        <v>345</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>20</v>
@@ -8134,7 +8124,7 @@
         <v>1852</v>
       </c>
       <c r="G149" s="4">
-        <f>(1+(F149-E149))-I149</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="H149" s="3" t="s">
@@ -8144,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>9</v>
@@ -8152,13 +8142,13 @@
       <c r="L149" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M149" s="31" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M149" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
-        <v>401</v>
+        <v>344</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>20</v>
@@ -8176,7 +8166,7 @@
         <v>1862</v>
       </c>
       <c r="G150" s="4">
-        <f>(1+(F150-E150))-I150</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="H150" s="3" t="s">
@@ -8186,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>9</v>
@@ -8194,13 +8184,13 @@
       <c r="L150" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M150" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M150" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>20</v>
@@ -8218,32 +8208,32 @@
         <v>1893</v>
       </c>
       <c r="G151" s="4">
-        <f>(1+(F151-E151))-I151</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="I151" s="4">
         <f>4</f>
         <v>4</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="L151" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M151" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M151" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>20</v>
@@ -8261,7 +8251,7 @@
         <v>1926</v>
       </c>
       <c r="G152" s="4">
-        <f>(1+(F152-E152))-I152</f>
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="H152" s="3" t="s">
@@ -8271,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K152" s="3" t="s">
         <v>9</v>
@@ -8279,13 +8269,13 @@
       <c r="L152" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M152" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M152" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>20</v>
@@ -8303,17 +8293,17 @@
         <v>1988</v>
       </c>
       <c r="G153" s="4">
-        <f>(1+(F153-E153))-I153</f>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="I153" s="4">
         <v>29</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>9</v>
@@ -8321,13 +8311,13 @@
       <c r="L153" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M153" s="11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M153" s="6" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>20</v>
@@ -8345,18 +8335,18 @@
         <v>2015</v>
       </c>
       <c r="G154" s="4">
-        <f>(1+(F154-E154))-I154</f>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="I154" s="4">
         <f>17+22</f>
         <v>39</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="K154" s="3" t="s">
         <v>9</v>
@@ -8364,13 +8354,13 @@
       <c r="L154" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M154" s="11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M154" s="6" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>20</v>
@@ -8388,7 +8378,7 @@
         <v>1864</v>
       </c>
       <c r="G155" s="4">
-        <f>(1+(F155-E155))-I155</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="H155" s="3" t="s">
@@ -8398,21 +8388,21 @@
         <v>0</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K155" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L155" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M155" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A156" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="M155" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A156" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>20</v>
@@ -8430,31 +8420,31 @@
         <v>1946</v>
       </c>
       <c r="G156" s="4">
-        <f>(1+(F156-E156))-I156</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I156" s="4">
         <v>58</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L156" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M156" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="157" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>20</v>
@@ -8472,7 +8462,7 @@
         <v>1892</v>
       </c>
       <c r="G157" s="4">
-        <f>(1+(F157-E157))-I157</f>
+        <f t="shared" ref="G157:G188" si="5">(1+(F157-E157))-I157</f>
         <v>21</v>
       </c>
       <c r="H157" s="3" t="s">
@@ -8482,29 +8472,26 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K157" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M157" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N157" s="10"/>
       <c r="O157" s="10"/>
       <c r="P157" s="10"/>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
-      <c r="S157" s="10"/>
-      <c r="T157" s="10"/>
-      <c r="U157" s="10"/>
-    </row>
-    <row r="158" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>20</v>
@@ -8522,7 +8509,7 @@
         <v>1932</v>
       </c>
       <c r="G158" s="4">
-        <f>(1+(F158-E158))-I158</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="H158" s="3" t="s">
@@ -8532,29 +8519,26 @@
         <v>0</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K158" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M158" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N158" s="10"/>
       <c r="O158" s="10"/>
       <c r="P158" s="10"/>
       <c r="Q158" s="10"/>
       <c r="R158" s="10"/>
-      <c r="S158" s="10"/>
-      <c r="T158" s="10"/>
-      <c r="U158" s="10"/>
-    </row>
-    <row r="159" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>20</v>
@@ -8572,39 +8556,36 @@
         <v>2000</v>
       </c>
       <c r="G159" s="4">
-        <f>(1+(F159-E159))-I159</f>
+        <f t="shared" si="5"/>
         <v>71</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="I159" s="4">
         <v>38</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K159" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M159" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N159" s="10"/>
       <c r="O159" s="10"/>
       <c r="P159" s="10"/>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
-      <c r="S159" s="10"/>
-      <c r="T159" s="10"/>
-      <c r="U159" s="10"/>
-    </row>
-    <row r="160" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>20</v>
@@ -8622,39 +8603,36 @@
         <v>2017</v>
       </c>
       <c r="G160" s="4">
-        <f>(1+(F160-E160))-I160</f>
+        <f t="shared" si="5"/>
         <v>170</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="I160" s="4">
         <v>5</v>
       </c>
       <c r="J160" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K160" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M160" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N160" s="10"/>
       <c r="O160" s="10"/>
       <c r="P160" s="10"/>
       <c r="Q160" s="10"/>
       <c r="R160" s="10"/>
-      <c r="S160" s="10"/>
-      <c r="T160" s="10"/>
-      <c r="U160" s="10"/>
-    </row>
-    <row r="161" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>20</v>
@@ -8672,7 +8650,7 @@
         <v>1943</v>
       </c>
       <c r="G161" s="4">
-        <f>(1+(F161-E161))-I161</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="H161" s="3" t="s">
@@ -8682,29 +8660,26 @@
         <v>0</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K161" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M161" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N161" s="10"/>
       <c r="O161" s="10"/>
       <c r="P161" s="10"/>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
-      <c r="S161" s="10"/>
-      <c r="T161" s="10"/>
-      <c r="U161" s="10"/>
-    </row>
-    <row r="162" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>20</v>
@@ -8722,39 +8697,36 @@
         <v>1974</v>
       </c>
       <c r="G162" s="4">
-        <f>(1+(F162-E162))-I162</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="I162" s="4">
         <v>71</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K162" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M162" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N162" s="10"/>
       <c r="O162" s="10"/>
       <c r="P162" s="10"/>
       <c r="Q162" s="10"/>
       <c r="R162" s="10"/>
-      <c r="S162" s="10"/>
-      <c r="T162" s="10"/>
-      <c r="U162" s="10"/>
-    </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>20</v>
@@ -8772,31 +8744,31 @@
         <v>1894</v>
       </c>
       <c r="G163" s="4">
-        <f>(1+(F163-E163))-I163</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="I163" s="4">
         <v>59</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K163" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M163" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>20</v>
@@ -8814,31 +8786,31 @@
         <v>1954</v>
       </c>
       <c r="G164" s="4">
-        <f>(1+(F164-E164))-I164</f>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="I164" s="4">
         <v>73</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K164" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M164" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>20</v>
@@ -8856,31 +8828,31 @@
         <v>1904</v>
       </c>
       <c r="G165" s="4">
-        <f>(1+(F165-E165))-I165</f>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I165" s="4">
         <v>20</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K165" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>20</v>
@@ -8898,31 +8870,31 @@
         <v>1985</v>
       </c>
       <c r="G166" s="4">
-        <f>(1+(F166-E166))-I166</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="I166" s="4">
         <v>2</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L166" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M166" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>20</v>
@@ -8940,7 +8912,7 @@
         <v>1924</v>
       </c>
       <c r="G167" s="4">
-        <f>(1+(F167-E167))-I167</f>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="H167" s="3" t="s">
@@ -8950,21 +8922,21 @@
         <v>0</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K167" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L167" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M167" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>20</v>
@@ -8982,7 +8954,7 @@
         <v>1933</v>
       </c>
       <c r="G168" s="4">
-        <f>(1+(F168-E168))-I168</f>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="H168" s="3" t="s">
@@ -8992,21 +8964,21 @@
         <v>0</v>
       </c>
       <c r="J168" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K168" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L168" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M168" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>20</v>
@@ -9024,7 +8996,7 @@
         <v>1890</v>
       </c>
       <c r="G169" s="4">
-        <f>(1+(F169-E169))-I169</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="H169" s="3" t="s">
@@ -9034,21 +9006,21 @@
         <v>0</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K169" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L169" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M169" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>20</v>
@@ -9066,7 +9038,7 @@
         <v>1933</v>
       </c>
       <c r="G170" s="4">
-        <f>(1+(F170-E170))-I170</f>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="H170" s="3" t="s">
@@ -9076,21 +9048,21 @@
         <v>0</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K170" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L170" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M170" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>20</v>
@@ -9108,7 +9080,7 @@
         <v>1933</v>
       </c>
       <c r="G171" s="4">
-        <f>(1+(F171-E171))-I171</f>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="H171" s="3" t="s">
@@ -9118,21 +9090,21 @@
         <v>0</v>
       </c>
       <c r="J171" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K171" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L171" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M171" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>20</v>
@@ -9150,7 +9122,7 @@
         <v>1908</v>
       </c>
       <c r="G172" s="4">
-        <f>(1+(F172-E172))-I172</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="H172" s="3" t="s">
@@ -9160,21 +9132,21 @@
         <v>0</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K172" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L172" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M172" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>20</v>
@@ -9192,7 +9164,7 @@
         <v>1933</v>
       </c>
       <c r="G173" s="4">
-        <f>(1+(F173-E173))-I173</f>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="H173" s="3" t="s">
@@ -9202,21 +9174,21 @@
         <v>0</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K173" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>20</v>
@@ -9234,7 +9206,7 @@
         <v>1933</v>
       </c>
       <c r="G174" s="4">
-        <f>(1+(F174-E174))-I174</f>
+        <f t="shared" si="5"/>
         <v>62</v>
       </c>
       <c r="H174" s="3" t="s">
@@ -9244,21 +9216,21 @@
         <v>0</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K174" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M174" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>20</v>
@@ -9276,7 +9248,7 @@
         <v>1921</v>
       </c>
       <c r="G175" s="4">
-        <f>(1+(F175-E175))-I175</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="H175" s="3" t="s">
@@ -9286,21 +9258,21 @@
         <v>0</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K175" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M175" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>20</v>
@@ -9318,7 +9290,7 @@
         <v>1924</v>
       </c>
       <c r="G176" s="4">
-        <f>(1+(F176-E176))-I176</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="H176" s="3" t="s">
@@ -9328,21 +9300,21 @@
         <v>0</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K176" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M176" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>20</v>
@@ -9360,31 +9332,31 @@
         <v>1928</v>
       </c>
       <c r="G177" s="4">
-        <f>(1+(F177-E177))-I177</f>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="I177" s="4">
         <v>37</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K177" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M177" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>20</v>
@@ -9402,31 +9374,31 @@
         <v>1890</v>
       </c>
       <c r="G178" s="4">
-        <f>(1+(F178-E178))-I178</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="I178" s="4">
         <v>34</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K178" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L178" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M178" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
-        <v>403</v>
+        <v>346</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>20</v>
@@ -9444,31 +9416,31 @@
         <v>1946</v>
       </c>
       <c r="G179" s="4">
-        <f>(1+(F179-E179))-I179</f>
+        <f t="shared" si="5"/>
         <v>79</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="I179" s="4">
         <v>19</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K179" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M179" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>20</v>
@@ -9486,31 +9458,31 @@
         <v>1953</v>
       </c>
       <c r="G180" s="4">
-        <f>(1+(F180-E180))-I180</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I180" s="4">
         <v>54</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K180" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M180" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>20</v>
@@ -9528,7 +9500,7 @@
         <v>1877</v>
       </c>
       <c r="G181" s="4">
-        <f>(1+(F181-E181))-I181</f>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="H181" s="3" t="s">
@@ -9538,21 +9510,21 @@
         <v>0</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K181" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L181" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M181" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>20</v>
@@ -9570,7 +9542,7 @@
         <v>1872</v>
       </c>
       <c r="G182" s="4">
-        <f>(1+(F182-E182))-I182</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="H182" s="3" t="s">
@@ -9580,21 +9552,21 @@
         <v>0</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K182" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M182" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="183" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>20</v>
@@ -9612,7 +9584,7 @@
         <v>1965</v>
       </c>
       <c r="G183" s="4">
-        <f>(1+(F183-E183))-I183</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="H183" s="3" t="s">
@@ -9622,29 +9594,26 @@
         <v>0</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K183" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="10"/>
       <c r="P183" s="10"/>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
-      <c r="S183" s="10"/>
-      <c r="T183" s="10"/>
-      <c r="U183" s="10"/>
-    </row>
-    <row r="184" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>20</v>
@@ -9662,39 +9631,36 @@
         <v>1952</v>
       </c>
       <c r="G184" s="4">
-        <f>(1+(F184-E184))-I184</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="I184" s="4">
         <v>87</v>
       </c>
       <c r="J184" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K184" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M184" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N184" s="10"/>
       <c r="O184" s="10"/>
       <c r="P184" s="10"/>
       <c r="Q184" s="10"/>
       <c r="R184" s="10"/>
-      <c r="S184" s="10"/>
-      <c r="T184" s="10"/>
-      <c r="U184" s="10"/>
-    </row>
-    <row r="185" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>20</v>
@@ -9712,7 +9678,7 @@
         <v>2017</v>
       </c>
       <c r="G185" s="4">
-        <f>(1+(F185-E185))-I185</f>
+        <f t="shared" si="5"/>
         <v>91</v>
       </c>
       <c r="H185" s="3" t="s">
@@ -9722,29 +9688,26 @@
         <v>25</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K185" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L185" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M185" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N185" s="10"/>
       <c r="O185" s="10"/>
       <c r="P185" s="10"/>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
-      <c r="S185" s="10"/>
-      <c r="T185" s="10"/>
-      <c r="U185" s="10"/>
-    </row>
-    <row r="186" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>20</v>
@@ -9762,7 +9725,7 @@
         <v>2017</v>
       </c>
       <c r="G186" s="4">
-        <f>(1+(F186-E186))-I186</f>
+        <f t="shared" si="5"/>
         <v>142</v>
       </c>
       <c r="H186" s="3" t="s">
@@ -9772,29 +9735,26 @@
         <v>0</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K186" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M186" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N186" s="10"/>
       <c r="O186" s="10"/>
       <c r="P186" s="10"/>
       <c r="Q186" s="10"/>
       <c r="R186" s="10"/>
-      <c r="S186" s="10"/>
-      <c r="T186" s="10"/>
-      <c r="U186" s="10"/>
-    </row>
-    <row r="187" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>20</v>
@@ -9812,7 +9772,7 @@
         <v>1914</v>
       </c>
       <c r="G187" s="4">
-        <f>(1+(F187-E187))-I187</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="H187" s="3" t="s">
@@ -9822,29 +9782,26 @@
         <v>0</v>
       </c>
       <c r="J187" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K187" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L187" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M187" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N187" s="10"/>
       <c r="O187" s="10"/>
       <c r="P187" s="10"/>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
-      <c r="S187" s="10"/>
-      <c r="T187" s="10"/>
-      <c r="U187" s="10"/>
-    </row>
-    <row r="188" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>20</v>
@@ -9862,39 +9819,36 @@
         <v>1928</v>
       </c>
       <c r="G188" s="4">
-        <f>(1+(F188-E188))-I188</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I188" s="4">
         <v>30</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K188" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L188" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M188" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N188" s="10"/>
       <c r="O188" s="10"/>
       <c r="P188" s="10"/>
       <c r="Q188" s="10"/>
       <c r="R188" s="10"/>
-      <c r="S188" s="10"/>
-      <c r="T188" s="10"/>
-      <c r="U188" s="10"/>
-    </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>20</v>
@@ -9912,32 +9866,32 @@
         <v>1973</v>
       </c>
       <c r="G189" s="4">
-        <f>(1+(F189-E189))-I189</f>
+        <f t="shared" ref="G189:G217" si="6">(1+(F189-E189))-I189</f>
         <v>43</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="I189" s="4">
         <f>16+8+15+12</f>
         <v>51</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L189" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M189" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>20</v>
@@ -9955,31 +9909,31 @@
         <v>1979</v>
       </c>
       <c r="G190" s="4">
-        <f>(1+(F190-E190))-I190</f>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I190" s="4">
         <v>6</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K190" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M190" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>20</v>
@@ -9997,7 +9951,7 @@
         <v>1949</v>
       </c>
       <c r="G191" s="4">
-        <f>(1+(F191-E191))-I191</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="H191" s="3" t="s">
@@ -10007,21 +9961,21 @@
         <v>0</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K191" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M191" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>20</v>
@@ -10039,7 +9993,7 @@
         <v>1919</v>
       </c>
       <c r="G192" s="4">
-        <f>(1+(F192-E192))-I192</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="H192" s="3" t="s">
@@ -10049,21 +10003,21 @@
         <v>0</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K192" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M192" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>20</v>
@@ -10081,7 +10035,7 @@
         <v>1943</v>
       </c>
       <c r="G193" s="4">
-        <f>(1+(F193-E193))-I193</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H193" s="3" t="s">
@@ -10091,21 +10045,21 @@
         <v>0</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K193" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M193" s="6" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>20</v>
@@ -10123,7 +10077,7 @@
         <v>2018</v>
       </c>
       <c r="G194" s="4">
-        <f>(1+(F194-E194))-I194</f>
+        <f t="shared" si="6"/>
         <v>98</v>
       </c>
       <c r="H194" s="3" t="s">
@@ -10133,21 +10087,21 @@
         <v>0</v>
       </c>
       <c r="J194" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K194" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M194" s="6" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
-        <v>404</v>
+        <v>347</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>20</v>
@@ -10165,7 +10119,7 @@
         <v>1827</v>
       </c>
       <c r="G195" s="4">
-        <f>(1+(F195-E195))-I195</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H195" s="3" t="s">
@@ -10175,21 +10129,21 @@
         <v>0</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K195" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M195" s="6" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>405</v>
+        <v>348</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>20</v>
@@ -10207,7 +10161,7 @@
         <v>1911</v>
       </c>
       <c r="G196" s="4">
-        <f>(1+(F196-E196))-I196</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="H196" s="3" t="s">
@@ -10217,21 +10171,21 @@
         <v>0</v>
       </c>
       <c r="J196" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K196" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L196" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M196" s="6" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
-        <v>406</v>
+        <v>349</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>20</v>
@@ -10249,7 +10203,7 @@
         <v>1877</v>
       </c>
       <c r="G197" s="4">
-        <f>(1+(F197-E197))-I197</f>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="H197" s="3" t="s">
@@ -10259,21 +10213,21 @@
         <v>0</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K197" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M197" s="6" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
-        <v>407</v>
+        <v>350</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>20</v>
@@ -10291,7 +10245,7 @@
         <v>1833</v>
       </c>
       <c r="G198" s="4">
-        <f>(1+(F198-E198))-I198</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H198" s="3" t="s">
@@ -10301,21 +10255,21 @@
         <v>0</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K198" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M198" s="6" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>20</v>
@@ -10333,7 +10287,7 @@
         <v>2018</v>
       </c>
       <c r="G199" s="4">
-        <f>(1+(F199-E199))-I199</f>
+        <f t="shared" si="6"/>
         <v>151</v>
       </c>
       <c r="H199" s="3" t="s">
@@ -10343,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="J199" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K199" s="3" t="s">
         <v>9</v>
@@ -10352,12 +10306,12 @@
         <v>79</v>
       </c>
       <c r="M199" s="6" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>20</v>
@@ -10375,17 +10329,17 @@
         <v>1952</v>
       </c>
       <c r="G200" s="4">
-        <f>(1+(F200-E200))-I200</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="I200" s="4">
         <v>32</v>
       </c>
       <c r="J200" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K200" s="3" t="s">
         <v>9</v>
@@ -10393,13 +10347,13 @@
       <c r="L200" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M200" s="5" t="s">
-        <v>362</v>
+      <c r="M200" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>20</v>
@@ -10417,17 +10371,17 @@
         <v>1958</v>
       </c>
       <c r="G201" s="4">
-        <f>(1+(F201-E201))-I201</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="I201" s="4">
         <v>18</v>
       </c>
       <c r="J201" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K201" s="3" t="s">
         <v>9</v>
@@ -10435,13 +10389,13 @@
       <c r="L201" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M201" s="5" t="s">
-        <v>362</v>
+      <c r="M201" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>20</v>
@@ -10459,7 +10413,7 @@
         <v>1932</v>
       </c>
       <c r="G202" s="4">
-        <f>(1+(F202-E202))-I202</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H202" s="3" t="s">
@@ -10469,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="J202" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K202" s="3" t="s">
         <v>9</v>
@@ -10477,13 +10431,13 @@
       <c r="L202" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M202" s="5" t="s">
-        <v>362</v>
+      <c r="M202" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>20</v>
@@ -10501,7 +10455,7 @@
         <v>1952</v>
       </c>
       <c r="G203" s="4">
-        <f>(1+(F203-E203))-I203</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H203" s="3" t="s">
@@ -10511,7 +10465,7 @@
         <v>0</v>
       </c>
       <c r="J203" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K203" s="3" t="s">
         <v>9</v>
@@ -10519,13 +10473,13 @@
       <c r="L203" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M203" s="5" t="s">
-        <v>362</v>
+      <c r="M203" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>20</v>
@@ -10543,7 +10497,7 @@
         <v>1918</v>
       </c>
       <c r="G204" s="4">
-        <f>(1+(F204-E204))-I204</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H204" s="3" t="s">
@@ -10553,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K204" s="3" t="s">
         <v>9</v>
@@ -10561,13 +10515,13 @@
       <c r="L204" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M204" s="5" t="s">
-        <v>362</v>
+      <c r="M204" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>20</v>
@@ -10585,7 +10539,7 @@
         <v>1952</v>
       </c>
       <c r="G205" s="4">
-        <f>(1+(F205-E205))-I205</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H205" s="3" t="s">
@@ -10595,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K205" s="3" t="s">
         <v>9</v>
@@ -10603,13 +10557,13 @@
       <c r="L205" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M205" s="5" t="s">
-        <v>362</v>
+      <c r="M205" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A206" s="28" t="s">
-        <v>155</v>
+      <c r="A206" t="s">
+        <v>154</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>20</v>
@@ -10627,31 +10581,31 @@
         <v>1890</v>
       </c>
       <c r="G206" s="4">
-        <f>(1+(F206-E206))-I206</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="I206" s="9">
         <v>24</v>
       </c>
       <c r="J206" s="8" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K206" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L206" s="14" t="s">
-        <v>205</v>
+      <c r="L206" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="M206" s="6" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A207" s="13" t="s">
-        <v>187</v>
+      <c r="A207" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>20</v>
@@ -10669,31 +10623,31 @@
         <v>1866</v>
       </c>
       <c r="G207" s="4">
-        <f>(1+(F207-E207))-I207</f>
+        <f t="shared" si="6"/>
         <v>1.42</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I207" s="9">
         <v>1.58</v>
       </c>
       <c r="J207" s="8" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K207" s="8" t="s">
         <v>21</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M207" s="6" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>20</v>
@@ -10711,11 +10665,11 @@
         <v>1946</v>
       </c>
       <c r="G208" s="4">
-        <f>(1+(F208-E208))-I208</f>
+        <f t="shared" si="6"/>
         <v>8.9000000000000057</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I208" s="9">
         <v>68.099999999999994</v>
@@ -10727,10 +10681,10 @@
         <v>21</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M208" s="6" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.35">
@@ -10753,7 +10707,7 @@
         <v>1876</v>
       </c>
       <c r="G209" s="4">
-        <f>(1+(F209-E209))-I209</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H209" s="3" t="s">
@@ -10763,26 +10717,26 @@
         <v>0</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="M209" s="5" t="s">
-        <v>365</v>
+        <v>212</v>
+      </c>
+      <c r="M209" s="6" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A210" s="28" t="s">
+      <c r="A210" t="s">
         <v>22</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C210" s="30">
+      <c r="C210" s="18">
         <v>46.197349000000003</v>
       </c>
       <c r="D210" s="4">
@@ -10795,17 +10749,17 @@
         <v>1876</v>
       </c>
       <c r="G210" s="4">
-        <f>(1+(F210-E210))-I210</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="I210" s="4">
         <v>3</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K210" s="3" t="s">
         <v>9</v>
@@ -10813,18 +10767,18 @@
       <c r="L210" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M210" s="5" t="s">
-        <v>365</v>
+      <c r="M210" s="6" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C211" s="30">
+      <c r="C211" s="18">
         <v>46.207951999999999</v>
       </c>
       <c r="D211" s="4">
@@ -10837,7 +10791,7 @@
         <v>1957</v>
       </c>
       <c r="G211" s="4">
-        <f>(1+(F211-E211))-I211</f>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="H211" s="8" t="s">
@@ -10847,26 +10801,26 @@
         <v>0</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L211" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M211" s="5" t="s">
-        <v>365</v>
+      <c r="M211" s="6" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C212" s="30">
+      <c r="C212" s="18">
         <v>46.170723000000002</v>
       </c>
       <c r="D212" s="4">
@@ -10879,7 +10833,7 @@
         <v>1942</v>
       </c>
       <c r="G212" s="4">
-        <f>(1+(F212-E212))-I212</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H212" s="3" t="s">
@@ -10889,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K212" s="3" t="s">
         <v>9</v>
@@ -10897,13 +10851,13 @@
       <c r="L212" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M212" s="5" t="s">
-        <v>365</v>
+      <c r="M212" s="6" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>20</v>
@@ -10921,7 +10875,7 @@
         <v>1943</v>
       </c>
       <c r="G213" s="4">
-        <f>(1+(F213-E213))-I213</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="H213" s="3" t="s">
@@ -10931,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="K213" s="3" t="s">
         <v>9</v>
@@ -10939,13 +10893,13 @@
       <c r="L213" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M213" s="5" t="s">
-        <v>365</v>
+      <c r="M213" s="6" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>20</v>
@@ -10963,7 +10917,7 @@
         <v>1897</v>
       </c>
       <c r="G214" s="4">
-        <f>(1+(F214-E214))-I214</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H214" s="3" t="s">
@@ -10973,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K214" s="3" t="s">
         <v>9</v>
@@ -10982,17 +10936,17 @@
         <v>15</v>
       </c>
       <c r="M214" s="6" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C215" s="30">
+      <c r="C215" s="18">
         <v>30.322700000000001</v>
       </c>
       <c r="D215" s="4">
@@ -11005,7 +10959,7 @@
         <v>1959</v>
       </c>
       <c r="G215" s="4">
-        <f>(1+(F215-E215))-I215</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H215" s="3" t="s">
@@ -11015,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K215" s="3" t="s">
         <v>9</v>
@@ -11024,12 +10978,12 @@
         <v>79</v>
       </c>
       <c r="M215" s="6" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>20</v>
@@ -11047,17 +11001,17 @@
         <v>1968</v>
       </c>
       <c r="G216" s="4">
-        <f>(1+(F216-E216))-I216</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="I216" s="4">
         <v>17</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K216" s="3" t="s">
         <v>9</v>
@@ -11066,12 +11020,12 @@
         <v>79</v>
       </c>
       <c r="M216" s="6" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
-        <v>408</v>
+        <v>351</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>20</v>
@@ -11089,17 +11043,17 @@
         <v>1892</v>
       </c>
       <c r="G217" s="4">
-        <f>(1+(F217-E217))-I217</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="I217" s="4">
         <v>12</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K217" s="3" t="s">
         <v>9</v>
@@ -11108,12 +11062,12 @@
         <v>21</v>
       </c>
       <c r="M217" s="6" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A218" s="13" t="s">
-        <v>248</v>
+      <c r="A218" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>20</v>
@@ -11124,10 +11078,10 @@
       <c r="D218" s="4">
         <v>-121.51</v>
       </c>
-      <c r="E218" s="17">
+      <c r="E218" s="15">
         <v>1919</v>
       </c>
-      <c r="F218" s="17">
+      <c r="F218" s="15">
         <f>E218+105</f>
         <v>2024</v>
       </c>
@@ -11138,11 +11092,11 @@
         <v>21</v>
       </c>
       <c r="I218" s="4">
-        <f>(F218-E218)-G218</f>
+        <f t="shared" ref="I218:I242" si="7">(F218-E218)-G218</f>
         <v>31</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K218" s="3" t="s">
         <v>9</v>
@@ -11151,12 +11105,12 @@
         <v>79</v>
       </c>
       <c r="M218" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A219" s="13" t="s">
-        <v>249</v>
+      <c r="A219" s="12" t="s">
+        <v>365</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>20</v>
@@ -11167,10 +11121,10 @@
       <c r="D219" s="4">
         <v>-121.53355999999999</v>
       </c>
-      <c r="E219" s="17">
+      <c r="E219" s="15">
         <v>1944</v>
       </c>
-      <c r="F219" s="17">
+      <c r="F219" s="15">
         <f>E219+80</f>
         <v>2024</v>
       </c>
@@ -11181,11 +11135,11 @@
         <v>21</v>
       </c>
       <c r="I219" s="4">
-        <f>(F219-E219)-G219</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K219" s="3" t="s">
         <v>9</v>
@@ -11194,12 +11148,12 @@
         <v>79</v>
       </c>
       <c r="M219" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A220" s="13" t="s">
-        <v>250</v>
+      <c r="A220" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>20</v>
@@ -11210,10 +11164,10 @@
       <c r="D220" s="4">
         <v>-121.44</v>
       </c>
-      <c r="E220" s="17">
+      <c r="E220" s="15">
         <v>1959</v>
       </c>
-      <c r="F220" s="17">
+      <c r="F220" s="15">
         <f>E220+65</f>
         <v>2024</v>
       </c>
@@ -11224,11 +11178,11 @@
         <v>21</v>
       </c>
       <c r="I220" s="4">
-        <f>(F220-E220)-G220</f>
+        <f t="shared" si="7"/>
         <v>2.8999999999999986</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K220" s="3" t="s">
         <v>9</v>
@@ -11237,12 +11191,12 @@
         <v>79</v>
       </c>
       <c r="M220" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A221" s="13" t="s">
-        <v>251</v>
+      <c r="A221" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>20</v>
@@ -11253,10 +11207,10 @@
       <c r="D221" s="4">
         <v>-121.51674</v>
       </c>
-      <c r="E221" s="17">
+      <c r="E221" s="15">
         <v>1929</v>
       </c>
-      <c r="F221" s="17">
+      <c r="F221" s="15">
         <f>E221+95</f>
         <v>2024</v>
       </c>
@@ -11267,11 +11221,11 @@
         <v>21</v>
       </c>
       <c r="I221" s="4">
-        <f>(F221-E221)-G221</f>
+        <f t="shared" si="7"/>
         <v>20.099999999999994</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K221" s="3" t="s">
         <v>9</v>
@@ -11280,12 +11234,12 @@
         <v>79</v>
       </c>
       <c r="M221" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A222" s="13" t="s">
-        <v>252</v>
+      <c r="A222" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>20</v>
@@ -11296,10 +11250,10 @@
       <c r="D222" s="4">
         <v>-121.4911</v>
       </c>
-      <c r="E222" s="17">
+      <c r="E222" s="15">
         <v>1925</v>
       </c>
-      <c r="F222" s="17">
+      <c r="F222" s="15">
         <f>E222+99</f>
         <v>2024</v>
       </c>
@@ -11310,11 +11264,11 @@
         <v>21</v>
       </c>
       <c r="I222" s="4">
-        <f>(F222-E222)-G222</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K222" s="3" t="s">
         <v>9</v>
@@ -11323,12 +11277,12 @@
         <v>79</v>
       </c>
       <c r="M222" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="27" t="s">
-        <v>253</v>
+      <c r="A223" s="24" t="s">
+        <v>369</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>20</v>
@@ -11339,10 +11293,10 @@
       <c r="D223" s="4">
         <v>-121.68639</v>
       </c>
-      <c r="E223" s="17">
+      <c r="E223" s="15">
         <v>1915</v>
       </c>
-      <c r="F223" s="17">
+      <c r="F223" s="15">
         <f>E223+109</f>
         <v>2024</v>
       </c>
@@ -11353,11 +11307,11 @@
         <v>21</v>
       </c>
       <c r="I223" s="4">
-        <f>(F223-E223)-G223</f>
+        <f t="shared" si="7"/>
         <v>30.299999999999997</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K223" s="3" t="s">
         <v>9</v>
@@ -11366,12 +11320,12 @@
         <v>79</v>
       </c>
       <c r="M223" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A224" s="13" t="s">
-        <v>254</v>
+      <c r="A224" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>20</v>
@@ -11382,10 +11336,10 @@
       <c r="D224" s="4">
         <v>-121.58389</v>
       </c>
-      <c r="E224" s="17">
+      <c r="E224" s="15">
         <v>1944</v>
       </c>
-      <c r="F224" s="17">
+      <c r="F224" s="15">
         <f>E224+80</f>
         <v>2024</v>
       </c>
@@ -11396,11 +11350,11 @@
         <v>21</v>
       </c>
       <c r="I224" s="4">
-        <f>(F224-E224)-G224</f>
+        <f t="shared" si="7"/>
         <v>16.799999999999997</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K224" s="3" t="s">
         <v>9</v>
@@ -11409,12 +11363,12 @@
         <v>79</v>
       </c>
       <c r="M224" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A225" s="13" t="s">
-        <v>255</v>
+      <c r="A225" s="12" t="s">
+        <v>371</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>20</v>
@@ -11425,10 +11379,10 @@
       <c r="D225" s="4">
         <v>-121.69917</v>
       </c>
-      <c r="E225" s="17">
+      <c r="E225" s="15">
         <v>1944</v>
       </c>
-      <c r="F225" s="17">
+      <c r="F225" s="15">
         <f>E225+40</f>
         <v>1984</v>
       </c>
@@ -11439,11 +11393,11 @@
         <v>21</v>
       </c>
       <c r="I225" s="4">
-        <f>(F225-E225)-G225</f>
+        <f t="shared" si="7"/>
         <v>14.100000000000001</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K225" s="3" t="s">
         <v>9</v>
@@ -11452,12 +11406,12 @@
         <v>79</v>
       </c>
       <c r="M225" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A226" s="16" t="s">
-        <v>256</v>
+      <c r="A226" s="14" t="s">
+        <v>372</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>20</v>
@@ -11468,10 +11422,10 @@
       <c r="D226" s="4">
         <v>-121.855</v>
       </c>
-      <c r="E226" s="17">
+      <c r="E226" s="15">
         <v>1915</v>
       </c>
-      <c r="F226" s="17">
+      <c r="F226" s="15">
         <f>E226+109</f>
         <v>2024</v>
       </c>
@@ -11482,11 +11436,11 @@
         <v>21</v>
       </c>
       <c r="I226" s="4">
-        <f>(F226-E226)-G226</f>
+        <f t="shared" si="7"/>
         <v>43.2</v>
       </c>
       <c r="J226" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K226" s="3" t="s">
         <v>9</v>
@@ -11495,12 +11449,12 @@
         <v>79</v>
       </c>
       <c r="M226" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A227" s="16" t="s">
-        <v>257</v>
+      <c r="A227" s="14" t="s">
+        <v>247</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>20</v>
@@ -11511,10 +11465,10 @@
       <c r="D227" s="4">
         <v>-122.14556</v>
       </c>
-      <c r="E227" s="17">
+      <c r="E227" s="15">
         <v>1944</v>
       </c>
-      <c r="F227" s="17">
+      <c r="F227" s="15">
         <f>E227+80</f>
         <v>2024</v>
       </c>
@@ -11525,11 +11479,11 @@
         <v>21</v>
       </c>
       <c r="I227" s="4">
-        <f>(F227-E227)-G227</f>
+        <f t="shared" si="7"/>
         <v>24.200000000000003</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K227" s="3" t="s">
         <v>9</v>
@@ -11538,12 +11492,12 @@
         <v>79</v>
       </c>
       <c r="M227" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A228" s="16" t="s">
-        <v>420</v>
+      <c r="A228" s="14" t="s">
+        <v>363</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>20</v>
@@ -11554,10 +11508,10 @@
       <c r="D228" s="4">
         <v>-121.80306</v>
       </c>
-      <c r="E228" s="17">
+      <c r="E228" s="15">
         <v>1934</v>
       </c>
-      <c r="F228" s="17">
+      <c r="F228" s="15">
         <f>E228+90</f>
         <v>2024</v>
       </c>
@@ -11568,11 +11522,11 @@
         <v>21</v>
       </c>
       <c r="I228" s="4">
-        <f>(F228-E228)-G228</f>
+        <f t="shared" si="7"/>
         <v>15.400000000000006</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K228" s="3" t="s">
         <v>9</v>
@@ -11581,12 +11535,12 @@
         <v>79</v>
       </c>
       <c r="M228" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A229" s="16" t="s">
-        <v>419</v>
+      <c r="A229" s="14" t="s">
+        <v>362</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>20</v>
@@ -11597,10 +11551,10 @@
       <c r="D229" s="4">
         <v>-121.59139</v>
       </c>
-      <c r="E229" s="17">
+      <c r="E229" s="15">
         <v>1957</v>
       </c>
-      <c r="F229" s="17">
+      <c r="F229" s="15">
         <f>E229+64</f>
         <v>2021</v>
       </c>
@@ -11611,11 +11565,11 @@
         <v>21</v>
       </c>
       <c r="I229" s="4">
-        <f>(F229-E229)-G229</f>
+        <f t="shared" si="7"/>
         <v>7.7000000000000028</v>
       </c>
       <c r="J229" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K229" s="3" t="s">
         <v>9</v>
@@ -11624,12 +11578,12 @@
         <v>79</v>
       </c>
       <c r="M229" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A230" s="16" t="s">
-        <v>418</v>
+      <c r="A230" s="14" t="s">
+        <v>361</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>20</v>
@@ -11640,10 +11594,10 @@
       <c r="D230" s="4">
         <v>-121.68694000000001</v>
       </c>
-      <c r="E230" s="17">
+      <c r="E230" s="15">
         <v>1944</v>
       </c>
-      <c r="F230" s="17">
+      <c r="F230" s="15">
         <f>E230+80</f>
         <v>2024</v>
       </c>
@@ -11654,11 +11608,11 @@
         <v>21</v>
       </c>
       <c r="I230" s="4">
-        <f>(F230-E230)-G230</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>9</v>
@@ -11667,12 +11621,12 @@
         <v>79</v>
       </c>
       <c r="M230" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A231" s="33" t="s">
-        <v>417</v>
+      <c r="A231" s="26" t="s">
+        <v>360</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>20</v>
@@ -11683,10 +11637,10 @@
       <c r="D231" s="4">
         <v>-121.49687</v>
       </c>
-      <c r="E231" s="17">
+      <c r="E231" s="15">
         <v>1928</v>
       </c>
-      <c r="F231" s="17">
+      <c r="F231" s="15">
         <f>E231+96</f>
         <v>2024</v>
       </c>
@@ -11697,11 +11651,11 @@
         <v>21</v>
       </c>
       <c r="I231" s="4">
-        <f>(F231-E231)-G231</f>
+        <f t="shared" si="7"/>
         <v>17.200000000000003</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K231" s="3" t="s">
         <v>9</v>
@@ -11710,12 +11664,12 @@
         <v>79</v>
       </c>
       <c r="M231" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A232" s="16" t="s">
-        <v>416</v>
+      <c r="A232" s="14" t="s">
+        <v>359</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>20</v>
@@ -11726,10 +11680,10 @@
       <c r="D232" s="4">
         <v>-121.52381</v>
       </c>
-      <c r="E232" s="17">
+      <c r="E232" s="15">
         <v>1957</v>
       </c>
-      <c r="F232" s="17">
+      <c r="F232" s="15">
         <f>E232+67</f>
         <v>2024</v>
       </c>
@@ -11740,11 +11694,11 @@
         <v>21</v>
       </c>
       <c r="I232" s="4">
-        <f>(F232-E232)-G232</f>
+        <f t="shared" si="7"/>
         <v>7.7999999999999972</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K232" s="3" t="s">
         <v>9</v>
@@ -11753,12 +11707,12 @@
         <v>79</v>
       </c>
       <c r="M232" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A233" s="16" t="s">
-        <v>415</v>
+      <c r="A233" s="14" t="s">
+        <v>358</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>20</v>
@@ -11769,10 +11723,10 @@
       <c r="D233" s="4">
         <v>-121.41943999999999</v>
       </c>
-      <c r="E233" s="17">
+      <c r="E233" s="15">
         <v>1939</v>
       </c>
-      <c r="F233" s="17">
+      <c r="F233" s="15">
         <f>E233+85</f>
         <v>2024</v>
       </c>
@@ -11783,11 +11737,11 @@
         <v>21</v>
       </c>
       <c r="I233" s="4">
-        <f>(F233-E233)-G233</f>
+        <f t="shared" si="7"/>
         <v>14.400000000000006</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K233" s="3" t="s">
         <v>9</v>
@@ -11796,12 +11750,12 @@
         <v>79</v>
       </c>
       <c r="M233" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A234" s="16" t="s">
-        <v>258</v>
+      <c r="A234" s="14" t="s">
+        <v>373</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>20</v>
@@ -11812,10 +11766,10 @@
       <c r="D234" s="4">
         <v>-121.58028</v>
       </c>
-      <c r="E234" s="17">
+      <c r="E234" s="15">
         <v>1945</v>
       </c>
-      <c r="F234" s="17">
+      <c r="F234" s="15">
         <f>E234+79</f>
         <v>2024</v>
       </c>
@@ -11826,11 +11780,11 @@
         <v>21</v>
       </c>
       <c r="I234" s="4">
-        <f>(F234-E234)-G234</f>
+        <f t="shared" si="7"/>
         <v>23.5</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K234" s="3" t="s">
         <v>9</v>
@@ -11839,12 +11793,12 @@
         <v>79</v>
       </c>
       <c r="M234" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A235" s="16" t="s">
-        <v>259</v>
+      <c r="A235" s="14" t="s">
+        <v>374</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>20</v>
@@ -11855,10 +11809,10 @@
       <c r="D235" s="4">
         <v>-121.36556</v>
       </c>
-      <c r="E235" s="17">
+      <c r="E235" s="15">
         <v>1959</v>
       </c>
-      <c r="F235" s="17">
+      <c r="F235" s="15">
         <f>E235+65</f>
         <v>2024</v>
       </c>
@@ -11869,11 +11823,11 @@
         <v>21</v>
       </c>
       <c r="I235" s="4">
-        <f>(F235-E235)-G235</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K235" s="3" t="s">
         <v>9</v>
@@ -11882,12 +11836,12 @@
         <v>79</v>
       </c>
       <c r="M235" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A236" s="16" t="s">
-        <v>260</v>
+      <c r="A236" s="14" t="s">
+        <v>375</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>20</v>
@@ -11898,10 +11852,10 @@
       <c r="D236" s="4">
         <v>-121.48833</v>
       </c>
-      <c r="E236" s="17">
+      <c r="E236" s="15">
         <v>1944</v>
       </c>
-      <c r="F236" s="17">
+      <c r="F236" s="15">
         <f>E236+80</f>
         <v>2024</v>
       </c>
@@ -11912,11 +11866,11 @@
         <v>21</v>
       </c>
       <c r="I236" s="4">
-        <f>(F236-E236)-G236</f>
+        <f t="shared" si="7"/>
         <v>10.599999999999994</v>
       </c>
       <c r="J236" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K236" s="3" t="s">
         <v>9</v>
@@ -11925,12 +11879,12 @@
         <v>79</v>
       </c>
       <c r="M236" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A237" s="16" t="s">
-        <v>414</v>
+      <c r="A237" s="14" t="s">
+        <v>357</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>20</v>
@@ -11941,10 +11895,10 @@
       <c r="D237" s="4">
         <v>-121.32308</v>
       </c>
-      <c r="E237" s="17">
+      <c r="E237" s="15">
         <v>1958</v>
       </c>
-      <c r="F237" s="17">
+      <c r="F237" s="15">
         <f>E237+66</f>
         <v>2024</v>
       </c>
@@ -11955,11 +11909,11 @@
         <v>21</v>
       </c>
       <c r="I237" s="4">
-        <f>(F237-E237)-G237</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K237" s="3" t="s">
         <v>9</v>
@@ -11968,12 +11922,12 @@
         <v>79</v>
       </c>
       <c r="M237" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A238" s="16" t="s">
-        <v>413</v>
+      <c r="A238" s="14" t="s">
+        <v>356</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>20</v>
@@ -11984,10 +11938,10 @@
       <c r="D238" s="4">
         <v>-121.38361</v>
       </c>
-      <c r="E238" s="17">
+      <c r="E238" s="15">
         <v>1958</v>
       </c>
-      <c r="F238" s="17">
+      <c r="F238" s="15">
         <f>E238+66</f>
         <v>2024</v>
       </c>
@@ -11998,11 +11952,11 @@
         <v>21</v>
       </c>
       <c r="I238" s="4">
-        <f>(F238-E238)-G238</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K238" s="3" t="s">
         <v>9</v>
@@ -12011,12 +11965,12 @@
         <v>79</v>
       </c>
       <c r="M238" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A239" s="16" t="s">
-        <v>412</v>
+      <c r="A239" s="14" t="s">
+        <v>355</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>20</v>
@@ -12027,10 +11981,10 @@
       <c r="D239" s="4">
         <v>-121.55301</v>
       </c>
-      <c r="E239" s="17">
+      <c r="E239" s="15">
         <v>1957</v>
       </c>
-      <c r="F239" s="17">
+      <c r="F239" s="15">
         <f>E239+67</f>
         <v>2024</v>
       </c>
@@ -12041,11 +11995,11 @@
         <v>21</v>
       </c>
       <c r="I239" s="4">
-        <f>(F239-E239)-G239</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K239" s="3" t="s">
         <v>9</v>
@@ -12054,12 +12008,12 @@
         <v>79</v>
       </c>
       <c r="M239" s="6" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A240" s="16" t="s">
-        <v>411</v>
+      <c r="A240" s="14" t="s">
+        <v>354</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>20</v>
@@ -12070,10 +12024,10 @@
       <c r="D240" s="4">
         <v>-121.44986</v>
       </c>
-      <c r="E240" s="17">
+      <c r="E240" s="15">
         <v>1958</v>
       </c>
-      <c r="F240" s="17">
+      <c r="F240" s="15">
         <f>E240+66</f>
         <v>2024</v>
       </c>
@@ -12084,11 +12038,11 @@
         <v>21</v>
       </c>
       <c r="I240" s="4">
-        <f>(F240-E240)-G240</f>
+        <f t="shared" si="7"/>
         <v>13.200000000000003</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K240" s="3" t="s">
         <v>9</v>
@@ -12097,12 +12051,12 @@
         <v>79</v>
       </c>
       <c r="M240" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A241" s="16" t="s">
-        <v>410</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A241" s="14" t="s">
+        <v>353</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>20</v>
@@ -12113,10 +12067,10 @@
       <c r="D241" s="4">
         <v>-121.44956000000001</v>
       </c>
-      <c r="E241" s="17">
+      <c r="E241" s="15">
         <v>1957</v>
       </c>
-      <c r="F241" s="17">
+      <c r="F241" s="15">
         <f>E241+67</f>
         <v>2024</v>
       </c>
@@ -12127,11 +12081,11 @@
         <v>21</v>
       </c>
       <c r="I241" s="4">
-        <f>(F241-E241)-G241</f>
+        <f t="shared" si="7"/>
         <v>5.5</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K241" s="3" t="s">
         <v>9</v>
@@ -12140,12 +12094,12 @@
         <v>79</v>
       </c>
       <c r="M241" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A242" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A242" s="14" t="s">
+        <v>352</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>20</v>
@@ -12156,10 +12110,10 @@
       <c r="D242" s="4">
         <v>-121.30649</v>
       </c>
-      <c r="E242" s="17">
+      <c r="E242" s="15">
         <v>1920</v>
       </c>
-      <c r="F242" s="17">
+      <c r="F242" s="15">
         <f>E242+104</f>
         <v>2024</v>
       </c>
@@ -12170,11 +12124,11 @@
         <v>21</v>
       </c>
       <c r="I242" s="4">
-        <f>(F242-E242)-G242</f>
+        <f t="shared" si="7"/>
         <v>58.2</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K242" s="3" t="s">
         <v>9</v>
@@ -12183,250 +12137,332 @@
         <v>79</v>
       </c>
       <c r="M242" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="243" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C243" s="20"/>
-      <c r="D243" s="20"/>
-      <c r="G243" s="20"/>
-      <c r="I243" s="20"/>
-    </row>
-    <row r="244" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C244" s="20"/>
-      <c r="D244" s="20"/>
-      <c r="G244" s="20"/>
-      <c r="I244" s="20"/>
-    </row>
-    <row r="245" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C245" s="20"/>
-      <c r="D245" s="20"/>
-      <c r="G245" s="20"/>
-      <c r="I245" s="20"/>
-    </row>
-    <row r="246" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C246" s="20"/>
-      <c r="D246" s="20"/>
-      <c r="G246" s="20"/>
-      <c r="I246" s="20"/>
-    </row>
-    <row r="247" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C247" s="20"/>
-      <c r="D247" s="20"/>
-      <c r="G247" s="20"/>
-      <c r="I247" s="20"/>
-    </row>
-    <row r="248" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C248" s="20"/>
-      <c r="D248" s="20"/>
-      <c r="G248" s="20"/>
-      <c r="I248" s="20"/>
-    </row>
-    <row r="249" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C249" s="20"/>
-      <c r="D249" s="20"/>
-      <c r="G249" s="20"/>
-      <c r="I249" s="20"/>
-    </row>
-    <row r="250" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C250" s="20"/>
-      <c r="D250" s="20"/>
-      <c r="G250" s="20"/>
-      <c r="I250" s="20"/>
-    </row>
-    <row r="251" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C251" s="20"/>
-      <c r="D251" s="20"/>
-      <c r="G251" s="20"/>
-      <c r="I251" s="20"/>
-    </row>
-    <row r="252" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C252" s="20"/>
-      <c r="D252" s="20"/>
-      <c r="G252" s="20"/>
-      <c r="I252" s="20"/>
-    </row>
-    <row r="253" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C253" s="20"/>
-      <c r="D253" s="20"/>
-      <c r="G253" s="20"/>
-      <c r="I253" s="20"/>
-    </row>
-    <row r="254" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C254" s="20"/>
-      <c r="D254" s="20"/>
-      <c r="G254" s="20"/>
-      <c r="I254" s="20"/>
-    </row>
-    <row r="255" spans="1:21" s="21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C255" s="22"/>
-      <c r="D255" s="22"/>
-      <c r="G255" s="22"/>
-      <c r="I255" s="22"/>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C243" s="18"/>
+      <c r="D243" s="18"/>
+      <c r="G243" s="18"/>
+      <c r="I243" s="18"/>
+    </row>
+    <row r="244" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C244" s="18"/>
+      <c r="D244" s="18"/>
+      <c r="G244" s="18"/>
+      <c r="I244" s="18"/>
+    </row>
+    <row r="245" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C245" s="18"/>
+      <c r="D245" s="18"/>
+      <c r="G245" s="18"/>
+      <c r="I245" s="18"/>
+    </row>
+    <row r="246" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C246" s="18"/>
+      <c r="D246" s="18"/>
+      <c r="G246" s="18"/>
+      <c r="I246" s="18"/>
+    </row>
+    <row r="247" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C247" s="18"/>
+      <c r="D247" s="18"/>
+      <c r="G247" s="18"/>
+      <c r="I247" s="18"/>
+    </row>
+    <row r="248" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C248" s="18"/>
+      <c r="D248" s="18"/>
+      <c r="G248" s="18"/>
+      <c r="I248" s="18"/>
+    </row>
+    <row r="249" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C249" s="18"/>
+      <c r="D249" s="18"/>
+      <c r="G249" s="18"/>
+      <c r="I249" s="18"/>
+    </row>
+    <row r="250" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C250" s="18"/>
+      <c r="D250" s="18"/>
+      <c r="G250" s="18"/>
+      <c r="I250" s="18"/>
+    </row>
+    <row r="251" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C251" s="18"/>
+      <c r="D251" s="18"/>
+      <c r="G251" s="18"/>
+      <c r="I251" s="18"/>
+    </row>
+    <row r="252" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C252" s="18"/>
+      <c r="D252" s="18"/>
+      <c r="G252" s="18"/>
+      <c r="I252" s="18"/>
+    </row>
+    <row r="253" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C253" s="18"/>
+      <c r="D253" s="18"/>
+      <c r="G253" s="18"/>
+      <c r="I253" s="18"/>
+    </row>
+    <row r="254" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C254" s="18"/>
+      <c r="D254" s="18"/>
+      <c r="G254" s="18"/>
+      <c r="I254" s="18"/>
+    </row>
+    <row r="255" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C255" s="20"/>
+      <c r="D255" s="20"/>
+      <c r="G255" s="20"/>
+      <c r="I255" s="20"/>
       <c r="N255"/>
       <c r="O255"/>
       <c r="P255"/>
       <c r="Q255"/>
       <c r="R255"/>
-      <c r="S255"/>
-      <c r="T255"/>
-      <c r="U255"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M73" r:id="rId1" xr:uid="{3156A7E3-978B-4D67-A0CA-485A3CB520BC}"/>
-    <hyperlink ref="M139" r:id="rId2" xr:uid="{DA15158E-3DEA-45E6-9B41-9836F1FBA791}"/>
-    <hyperlink ref="M124" r:id="rId3" xr:uid="{CD90CD5C-121B-40CE-86EC-9AE671E50AF0}"/>
-    <hyperlink ref="M8" r:id="rId4" xr:uid="{CB0A140F-6848-4561-99A2-2630BD2640CF}"/>
-    <hyperlink ref="M114" r:id="rId5" xr:uid="{F580041F-B2FD-4531-B494-2E6AAFC5279F}"/>
-    <hyperlink ref="M41" r:id="rId6" xr:uid="{50750C0F-6BA2-45EB-A958-9298489232F9}"/>
-    <hyperlink ref="M24" r:id="rId7" xr:uid="{F56B0A45-15FD-4D61-AD34-DBB23D62CC12}"/>
-    <hyperlink ref="M100" r:id="rId8" xr:uid="{7251189B-5D09-451F-A7D8-EB35396A3A93}"/>
-    <hyperlink ref="M25" r:id="rId9" xr:uid="{6802BF4D-8A74-44DF-867D-E8907E44EF30}"/>
-    <hyperlink ref="M101" r:id="rId10" xr:uid="{9E99DD31-258E-4AA8-BC2E-EFEDC268147E}"/>
-    <hyperlink ref="M96" r:id="rId11" location="s0010" xr:uid="{6BE3E221-D9BB-457D-8CA2-0BB45F6D399D}"/>
-    <hyperlink ref="M148" r:id="rId12" xr:uid="{5FDCDE20-3A89-42E1-A91B-3199D6A91AD4}"/>
-    <hyperlink ref="M49" r:id="rId13" xr:uid="{C40DF6EF-C197-4467-AB2E-660CCDDAB55C}"/>
-    <hyperlink ref="M119" r:id="rId14" xr:uid="{4B35C2B7-F273-4541-ADBB-10AEE30FF055}"/>
-    <hyperlink ref="M78" r:id="rId15" location="Sec2" xr:uid="{ACEC51D4-2FC4-4507-9673-CC184939B1D3}"/>
-    <hyperlink ref="M209" r:id="rId16" xr:uid="{9FCB400D-13B4-45C3-BB35-E1CBD56EACFE}"/>
-    <hyperlink ref="M55" r:id="rId17" xr:uid="{C8811510-C290-4E5F-B3CB-63B5093F5755}"/>
-    <hyperlink ref="M104" r:id="rId18" xr:uid="{BB1C8349-7CB9-4112-8D53-B5139CBB6EA4}"/>
-    <hyperlink ref="M123" r:id="rId19" xr:uid="{FF9ABB49-4A4E-47FB-A381-B935DFFC747F}"/>
-    <hyperlink ref="M153" r:id="rId20" xr:uid="{1A5C9112-4F23-484A-8555-8FE8523F3551}"/>
-    <hyperlink ref="M54" r:id="rId21" xr:uid="{010269A2-BCB3-49AC-9C2C-0C6709F27B1D}"/>
-    <hyperlink ref="M44" r:id="rId22" location="s0010" xr:uid="{93B3E189-E072-4495-8E00-DA81FCC38006}"/>
-    <hyperlink ref="M71" r:id="rId23" location="section2" xr:uid="{840B5D32-EDFD-4948-9559-230EA8341A32}"/>
-    <hyperlink ref="M61" r:id="rId24" xr:uid="{5D848213-6539-4F39-827F-144D8C42B8DE}"/>
-    <hyperlink ref="M214" r:id="rId25" xr:uid="{ABFA4308-264D-4DE3-8242-8BD0A8736E59}"/>
-    <hyperlink ref="M155" r:id="rId26" xr:uid="{E414BA2C-1F50-4C21-8B46-A64C02D16878}"/>
-    <hyperlink ref="M145" r:id="rId27" xr:uid="{D8397285-549C-4627-8F28-4D0DCB0DE3F3}"/>
-    <hyperlink ref="M86" r:id="rId28" xr:uid="{0EC325D1-1BF5-4628-BC62-9E6C16E040CE}"/>
-    <hyperlink ref="M64" r:id="rId29" xr:uid="{B87782F1-E111-4E04-846C-2A4DEFB910F8}"/>
-    <hyperlink ref="M68" r:id="rId30" xr:uid="{F21D65F2-9489-4C0C-8C79-B55892F8B99D}"/>
-    <hyperlink ref="M3" r:id="rId31" xr:uid="{D310EA37-8EAD-4589-8B97-8842B6006557}"/>
-    <hyperlink ref="M26" r:id="rId32" xr:uid="{966C93A3-3B03-46EE-9C33-312EC5E24C43}"/>
-    <hyperlink ref="M74" r:id="rId33" location="tocto1n3" xr:uid="{A7C4F35F-6EF2-454C-A5CD-7CB4A811C143}"/>
-    <hyperlink ref="M81" r:id="rId34" xr:uid="{9C58A15B-7147-49BD-92F5-E4BD14E45375}"/>
-    <hyperlink ref="M42" r:id="rId35" xr:uid="{FAEA354F-ED1A-4263-B0B1-F8845D038FFC}"/>
-    <hyperlink ref="M40" r:id="rId36" location="sec2" xr:uid="{A99ABD7F-E763-4BDA-86D1-27BAC3C5339D}"/>
-    <hyperlink ref="M2" r:id="rId37" xr:uid="{A665216B-43F9-45FA-AAAB-02644618C923}"/>
-    <hyperlink ref="M52" r:id="rId38" xr:uid="{82E183EA-885E-4609-8B92-BF5AF88FE381}"/>
-    <hyperlink ref="M206" r:id="rId39" xr:uid="{9DB841F1-BDF5-41E0-96D6-B0215632F8F1}"/>
-    <hyperlink ref="M218" r:id="rId40" xr:uid="{E0AD1488-5E66-4401-A1DB-571A7EA64B28}"/>
-    <hyperlink ref="M63" r:id="rId41" xr:uid="{D3C535B0-BC03-4AA8-BC80-CAA439EA5825}"/>
-    <hyperlink ref="M146" r:id="rId42" xr:uid="{FA31B7FC-54F4-4271-A62A-485C6372FBC0}"/>
-    <hyperlink ref="M158:M159" r:id="rId43" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{CE65E876-FBDD-4290-A4B8-8DFB06F67E3B}"/>
-    <hyperlink ref="M62" r:id="rId44" xr:uid="{4E1FB74D-38C6-4D78-AE35-D734112D13E9}"/>
-    <hyperlink ref="M9" r:id="rId45" xr:uid="{36B4C0F7-3F45-404F-A3B2-279AA63B252E}"/>
-    <hyperlink ref="M140" r:id="rId46" xr:uid="{09550023-6696-4274-8BDE-82B2B761E196}"/>
-    <hyperlink ref="M90" r:id="rId47" xr:uid="{6B02A3D3-7ED4-4F19-B40A-719643155801}"/>
-    <hyperlink ref="M6:M35" r:id="rId48" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{F02AC363-39FA-4DE5-96D4-1825E567D45E}"/>
-    <hyperlink ref="M144" r:id="rId49" xr:uid="{DF92C435-AD58-4C3B-A764-EFEF33C8306D}"/>
-    <hyperlink ref="M143" r:id="rId50" xr:uid="{7EBFE8E4-9A34-49FD-A506-6AC75779AD70}"/>
-    <hyperlink ref="M3:M4" r:id="rId51" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{36CE401B-52C3-465B-8F52-BA0E9BAD14FD}"/>
-    <hyperlink ref="M33" r:id="rId52" xr:uid="{E6677CAD-EDEE-4F44-B993-05ADE913804D}"/>
-    <hyperlink ref="M34" r:id="rId53" xr:uid="{249DD78B-159F-42E8-9E8D-40C69F78CB87}"/>
-    <hyperlink ref="M35" r:id="rId54" xr:uid="{880A7659-7317-4ACD-810B-3C090496C90B}"/>
-    <hyperlink ref="M36" r:id="rId55" xr:uid="{54FED2B1-F082-429D-B4CE-3D76FD2D8ECD}"/>
-    <hyperlink ref="M37" r:id="rId56" xr:uid="{7B2AD819-DABB-49C2-943E-AD6B7BAC4916}"/>
-    <hyperlink ref="M75" r:id="rId57" location="tocto1n3" xr:uid="{11C10A2C-5AFE-49E1-A419-D15183877D25}"/>
-    <hyperlink ref="M76" r:id="rId58" location="tocto1n3" xr:uid="{36B0B5FA-9DE8-4E99-B898-A60528D3B38A}"/>
-    <hyperlink ref="M77" r:id="rId59" location="tocto1n3" xr:uid="{FF6E229C-6B83-4B38-B50C-CA1DF8463A4D}"/>
-    <hyperlink ref="M38" r:id="rId60" location="tocto1n3" xr:uid="{DF89BA1A-460A-4360-B2B5-9040E39AB03A}"/>
-    <hyperlink ref="M39" r:id="rId61" location="tocto1n3" xr:uid="{F3C26987-5A9E-4085-A1AD-9395837B96A0}"/>
-    <hyperlink ref="M115" r:id="rId62" xr:uid="{55C7649D-0F8E-48C8-A8E7-1286CEE711BC}"/>
-    <hyperlink ref="M116" r:id="rId63" xr:uid="{43DCC5C4-EAA0-4397-92FC-DFEC882AD296}"/>
-    <hyperlink ref="M117" r:id="rId64" xr:uid="{2FC77281-A231-4D27-A1DE-15938B9BD884}"/>
-    <hyperlink ref="M118" r:id="rId65" xr:uid="{DAFFC5EA-0273-4DEE-9272-D54D3E117308}"/>
-    <hyperlink ref="M43" r:id="rId66" xr:uid="{9771A565-7528-46B2-B765-A06D853CF94D}"/>
-    <hyperlink ref="M102" r:id="rId67" xr:uid="{C86F1D59-C579-486C-B277-46A930EE0ADA}"/>
-    <hyperlink ref="M103" r:id="rId68" xr:uid="{9ED9452E-5C3E-44CD-8CFF-C9A0D2BC47E8}"/>
-    <hyperlink ref="M45" r:id="rId69" location="s0010" xr:uid="{F6C56819-5742-47C7-A15D-1E938CC75CC0}"/>
-    <hyperlink ref="M46" r:id="rId70" location="s0010" xr:uid="{54D53B13-64AF-4271-81A7-E12FA9382D8F}"/>
-    <hyperlink ref="M47" r:id="rId71" location="s0010" xr:uid="{45143C87-709A-4255-BA3F-9D5EBBD396E4}"/>
-    <hyperlink ref="M48" r:id="rId72" location="s0010" xr:uid="{59CF8832-6414-4A4A-9E3D-31E971D61704}"/>
-    <hyperlink ref="M65" r:id="rId73" xr:uid="{AC6A8081-3A8F-4A2B-B2D9-4988AE539BFE}"/>
-    <hyperlink ref="M4" r:id="rId74" xr:uid="{0364716F-7036-44B1-AFFC-EAA5C3E2A558}"/>
-    <hyperlink ref="M5" r:id="rId75" xr:uid="{9027C3EB-9813-48BF-AD4D-5116A43FB727}"/>
-    <hyperlink ref="M6" r:id="rId76" xr:uid="{02803618-7350-4331-9D2D-5B9827512019}"/>
-    <hyperlink ref="M7" r:id="rId77" xr:uid="{0E98C3FD-5512-43D0-8196-32779E4C7FB7}"/>
-    <hyperlink ref="M82:M88" r:id="rId78" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{DBACA97B-8121-4087-91C5-C00614750180}"/>
-    <hyperlink ref="M149" r:id="rId79" xr:uid="{EAC7B0A5-B15C-4C74-9CC0-EAD4E5D06C63}"/>
-    <hyperlink ref="M150" r:id="rId80" xr:uid="{FDA81486-5AA8-41DF-9163-D1396DC141AE}"/>
-    <hyperlink ref="M151" r:id="rId81" xr:uid="{348D3B28-5430-4A9D-9665-11CA6AC2F314}"/>
-    <hyperlink ref="M152" r:id="rId82" xr:uid="{8AB3BB7E-6790-470F-97E0-06731480DAB9}"/>
-    <hyperlink ref="M50" r:id="rId83" xr:uid="{20190AE3-90FD-4B5D-ABCB-2102C2C101DC}"/>
-    <hyperlink ref="M51" r:id="rId84" xr:uid="{427F129C-6852-4CE4-B4C8-028156226966}"/>
-    <hyperlink ref="M120" r:id="rId85" xr:uid="{E805B08C-2EA7-48BB-B20E-86EA79C479B2}"/>
-    <hyperlink ref="M121" r:id="rId86" xr:uid="{7DF258B2-5960-4F00-BEF8-C2B5F0E20846}"/>
-    <hyperlink ref="M122" r:id="rId87" xr:uid="{203FB33D-37E5-40A0-83A4-54B0A5053920}"/>
-    <hyperlink ref="M53" r:id="rId88" xr:uid="{4776D7AB-FA4A-4D73-8EE1-718AB53B89D3}"/>
-    <hyperlink ref="M154" r:id="rId89" xr:uid="{03C46567-31A1-4306-8D53-1E59A3B47F8E}"/>
-    <hyperlink ref="M106:M143" r:id="rId90" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{35D97555-7EF5-4E0C-B46C-E100FEE0E8C2}"/>
-    <hyperlink ref="M194" r:id="rId91" xr:uid="{8E32E9AC-0D10-4DBE-8B47-42A41ECE877D}"/>
-    <hyperlink ref="M195" r:id="rId92" xr:uid="{11DFC79D-5E39-4CD5-9B31-E516E665B932}"/>
-    <hyperlink ref="M196" r:id="rId93" xr:uid="{9509BE69-A7AB-4464-9762-F5E81CADA3E1}"/>
-    <hyperlink ref="M197" r:id="rId94" xr:uid="{48442C5F-D04D-4B94-9B38-F134E9271BCC}"/>
-    <hyperlink ref="M198" r:id="rId95" xr:uid="{9657C4EE-FC54-482B-BA56-33662914B22B}"/>
-    <hyperlink ref="M199" r:id="rId96" xr:uid="{EBA090C5-776B-44CD-84B4-0C2267F908E0}"/>
-    <hyperlink ref="M200" r:id="rId97" xr:uid="{22B3FCB0-9D6D-4652-B3B0-08D0715F0E40}"/>
-    <hyperlink ref="M201" r:id="rId98" xr:uid="{E8B94AFC-73D6-48A4-83CD-FDBBDD6AAEDA}"/>
-    <hyperlink ref="M202" r:id="rId99" xr:uid="{E1546CB7-DAEC-41D1-B0C0-D1B7CA766194}"/>
-    <hyperlink ref="M203" r:id="rId100" xr:uid="{2CA61BBE-1E0D-4B76-804A-239957BCA421}"/>
-    <hyperlink ref="M204" r:id="rId101" xr:uid="{45962396-12DD-4723-9D3C-03823E32D588}"/>
-    <hyperlink ref="M205" r:id="rId102" xr:uid="{635E4791-CBE8-4207-8D7E-A8A39B6009FF}"/>
-    <hyperlink ref="M79" r:id="rId103" location="Sec2" xr:uid="{A919E4DB-D431-432E-AD83-64403D035E8F}"/>
-    <hyperlink ref="M80" r:id="rId104" location="Sec2" xr:uid="{7ADFE268-0A90-4125-85F9-725A44392DA7}"/>
-    <hyperlink ref="M207" r:id="rId105" xr:uid="{703E4408-7911-4C12-B279-56C99926F0E4}"/>
-    <hyperlink ref="M208" r:id="rId106" xr:uid="{D86BE662-3167-4FD4-B681-5BF7C5D107C6}"/>
-    <hyperlink ref="M210" r:id="rId107" xr:uid="{06E13893-963C-4F0A-BF48-4290EF94A58C}"/>
-    <hyperlink ref="M211" r:id="rId108" xr:uid="{E9AED0E5-239B-46C7-AD4D-A347606D88F1}"/>
-    <hyperlink ref="M212" r:id="rId109" xr:uid="{F7C50425-CF51-4B57-8CC6-8F446853450F}"/>
-    <hyperlink ref="M213" r:id="rId110" xr:uid="{12ACFB7D-94FC-4D7B-8426-6E89E261CAC9}"/>
-    <hyperlink ref="M56" r:id="rId111" xr:uid="{2D05E89F-9E6E-40F4-8046-580F5EA4F4B5}"/>
-    <hyperlink ref="M57" r:id="rId112" xr:uid="{A0917417-EDCB-4724-863E-6A45B6C717F3}"/>
-    <hyperlink ref="M58" r:id="rId113" xr:uid="{5CEC15DA-5E21-4EC3-8BE2-00130A26FDA7}"/>
-    <hyperlink ref="M59" r:id="rId114" xr:uid="{6135267F-C152-48FA-8404-96C8D819B09A}"/>
-    <hyperlink ref="M60" r:id="rId115" xr:uid="{E6A303D7-2EBA-436A-898A-EB0D11A905D4}"/>
-    <hyperlink ref="M105" r:id="rId116" xr:uid="{84548A19-6042-4A4B-AFEE-0F6A44601FB7}"/>
-    <hyperlink ref="M106" r:id="rId117" xr:uid="{86416050-C685-4FA3-97DB-538F669FCE0E}"/>
-    <hyperlink ref="M107" r:id="rId118" xr:uid="{32F763E9-4D59-44B2-8501-F68783BF678C}"/>
-    <hyperlink ref="M108" r:id="rId119" xr:uid="{BA8C6504-56F6-441F-B891-E7754BD8D46A}"/>
-    <hyperlink ref="M109" r:id="rId120" xr:uid="{8492308A-C904-40F0-840C-3E3A7E8BB294}"/>
-    <hyperlink ref="M110" r:id="rId121" xr:uid="{C913FF9D-6F94-41CE-AE66-FE77ECDFC72E}"/>
-    <hyperlink ref="M111" r:id="rId122" xr:uid="{105FDA06-8805-4F44-8764-ACB489CA1DF0}"/>
-    <hyperlink ref="M215" r:id="rId123" xr:uid="{E60DDDBE-84A5-4B5A-A2F0-AF9CA4844DB0}"/>
-    <hyperlink ref="M216" r:id="rId124" xr:uid="{9E841500-D1FC-45BD-A532-0EC98129388A}"/>
-    <hyperlink ref="M217" r:id="rId125" xr:uid="{B8C855F4-45CB-4B4E-A732-6B854E76C1DF}"/>
-    <hyperlink ref="M72" r:id="rId126" location="section2" xr:uid="{1E0D5D5A-1B92-45DC-AF39-6951426F61F0}"/>
-    <hyperlink ref="M190:M203" r:id="rId127" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{C99BE9B1-BA0D-4BE1-A342-467B058900B4}"/>
-    <hyperlink ref="M219" r:id="rId128" xr:uid="{AE59D820-48B1-4F19-98A6-31BC0F6185C4}"/>
-    <hyperlink ref="M220" r:id="rId129" xr:uid="{4FC1E65E-95A4-4A01-81BA-3AF476A6B8CB}"/>
-    <hyperlink ref="M221" r:id="rId130" xr:uid="{84825A96-32B3-4F4C-B6F9-DD88109A82C6}"/>
-    <hyperlink ref="M222" r:id="rId131" xr:uid="{48B43ECA-2362-4898-82F7-A281E824DA2B}"/>
-    <hyperlink ref="M223" r:id="rId132" xr:uid="{86C470D1-05B0-466B-88C3-BCE82A400DAF}"/>
-    <hyperlink ref="M224" r:id="rId133" xr:uid="{43676997-31BD-46F9-AB41-0D07C4B82F3F}"/>
-    <hyperlink ref="M225" r:id="rId134" xr:uid="{0B4CCF44-8969-4A6B-B7B0-394DF7507560}"/>
-    <hyperlink ref="M226" r:id="rId135" xr:uid="{849CC153-59C7-437C-8E3A-D63E77367CB6}"/>
-    <hyperlink ref="M227" r:id="rId136" xr:uid="{F2B7F12F-2917-4B95-978F-AB05D13AC628}"/>
-    <hyperlink ref="M228" r:id="rId137" xr:uid="{137A4936-4B90-4C82-B808-F5F252316902}"/>
-    <hyperlink ref="M229" r:id="rId138" xr:uid="{B60AED1B-154B-456F-BC0E-7519E10FE080}"/>
-    <hyperlink ref="M230" r:id="rId139" xr:uid="{C890BA5E-1295-42C3-AAA8-E478CC315A62}"/>
-    <hyperlink ref="M242" r:id="rId140" xr:uid="{CF382673-A9E9-4E52-BD68-BBB5F8D5FBBB}"/>
-    <hyperlink ref="M241" r:id="rId141" xr:uid="{F4C4FBA2-E34D-4EDE-829F-F188A1AB0FD8}"/>
-    <hyperlink ref="M240" r:id="rId142" xr:uid="{46E72D9A-E4D8-47CF-90E2-E71B5C0F4F0C}"/>
-    <hyperlink ref="M239" r:id="rId143" xr:uid="{1FD3A41D-04D9-4B94-AAB2-EFDB4F57A545}"/>
-    <hyperlink ref="M238" r:id="rId144" xr:uid="{48AE7924-1FCC-480E-ABDC-F0DD49BC0443}"/>
-    <hyperlink ref="M237" r:id="rId145" xr:uid="{E9102FA3-7DE9-403D-8D2A-4E6E2CEC276E}"/>
-    <hyperlink ref="M236" r:id="rId146" xr:uid="{96470856-1EE6-4148-8AB0-FF6677A23AFC}"/>
-    <hyperlink ref="M235" r:id="rId147" xr:uid="{FCC5B73A-C3FF-48EE-954B-6D99F598BAE4}"/>
-    <hyperlink ref="M234" r:id="rId148" xr:uid="{0C407A72-2621-4B1A-85D2-3CCF5B93F160}"/>
-    <hyperlink ref="M233" r:id="rId149" xr:uid="{8BAB84E9-A1A1-48E8-952A-FD1B152AEF5C}"/>
-    <hyperlink ref="M232" r:id="rId150" xr:uid="{04A930E8-8072-4203-8EA8-030354B5DD0F}"/>
-    <hyperlink ref="M231" r:id="rId151" xr:uid="{45E58B22-1AF2-4040-A0BE-02CAB47A5000}"/>
-    <hyperlink ref="M91" r:id="rId152" xr:uid="{28373673-5A66-454F-850D-46473D27222E}"/>
-    <hyperlink ref="M92" r:id="rId153" xr:uid="{1C7D7281-E554-426F-AD8A-9E32CB0CAD49}"/>
+    <hyperlink ref="M24" r:id="rId1" xr:uid="{F56B0A45-15FD-4D61-AD34-DBB23D62CC12}"/>
+    <hyperlink ref="M2" r:id="rId2" display="https://academic.oup.com/gji/article/182/2/781/571033" xr:uid="{32927651-0D28-4422-9EC0-5AF2E688D7D1}"/>
+    <hyperlink ref="M3" r:id="rId3" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{7382E448-BC55-4FBD-A344-282BF3B24369}"/>
+    <hyperlink ref="M4" r:id="rId4" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{F986631E-5216-498C-86FA-F5CC5E73664D}"/>
+    <hyperlink ref="M5" r:id="rId5" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{7F716E74-FCC9-4E7E-A616-A92813652EEF}"/>
+    <hyperlink ref="M6" r:id="rId6" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{D02BBF79-A00C-41AD-B807-62E5CC711F5E}"/>
+    <hyperlink ref="M7" r:id="rId7" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{6121B0E0-FDC1-4542-B692-3775E17CFEEF}"/>
+    <hyperlink ref="M8" r:id="rId8" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908" xr:uid="{C9CA88CA-C7EB-4A3B-A315-458CBB6E1A30}"/>
+    <hyperlink ref="M9" r:id="rId9" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908" xr:uid="{F484B450-D1CD-4F83-99FC-818BAF6FB4F7}"/>
+    <hyperlink ref="M11" r:id="rId10" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{25622AF0-096B-4358-B52B-19F3BB04AF0F}"/>
+    <hyperlink ref="M12" r:id="rId11" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{B4E3903C-6A25-4FC2-95B5-2FA5D1472727}"/>
+    <hyperlink ref="M13" r:id="rId12" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{2C0B238A-7D21-4C6E-93B6-8338FA0E76F2}"/>
+    <hyperlink ref="M14" r:id="rId13" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{8DD35A58-70A1-4A05-AAC9-0DF8A82FE4B3}"/>
+    <hyperlink ref="M15" r:id="rId14" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{BFD0F7D0-D497-46EE-9552-482CD1EC46C6}"/>
+    <hyperlink ref="M16" r:id="rId15" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{D0B17AB9-6417-48C2-8EDE-334B93ACC604}"/>
+    <hyperlink ref="M17" r:id="rId16" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{30AC0A4A-11B3-4674-A437-4E1432982B71}"/>
+    <hyperlink ref="M18" r:id="rId17" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{B7421E68-69C5-40F2-92BB-5E25235266F2}"/>
+    <hyperlink ref="M19" r:id="rId18" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{93A19547-7BA8-4569-9060-5998C8042EBC}"/>
+    <hyperlink ref="M20" r:id="rId19" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{C630A410-DB0B-4992-B232-580421EAAE0F}"/>
+    <hyperlink ref="M21" r:id="rId20" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{2383A804-D072-407C-8DF3-EF914F91FA30}"/>
+    <hyperlink ref="M22" r:id="rId21" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{276CC7E3-E94F-46D4-9B37-C8A50333A8BA}"/>
+    <hyperlink ref="M23" r:id="rId22" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{CCCD7318-15BC-4579-8B7E-D5099A5D0EA3}"/>
+    <hyperlink ref="M26" r:id="rId23" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{27D303E9-1AE6-4B69-AAAE-69B0783E0D6D}"/>
+    <hyperlink ref="M10" r:id="rId24" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{662BD8C2-C9A8-4821-AE66-ED99159A86DB}"/>
+    <hyperlink ref="M27" r:id="rId25" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{47B4547F-7B7D-41EA-B3A5-FCF8E1DB0F15}"/>
+    <hyperlink ref="M28" r:id="rId26" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{96377C57-C4D6-4667-B1E0-6E34FD748311}"/>
+    <hyperlink ref="M29" r:id="rId27" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{664F0AF7-D9DE-4D26-8655-EE8F57727D5D}"/>
+    <hyperlink ref="M30" r:id="rId28" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{C89C3DF6-3A69-4287-8144-DDBFAAFB16EB}"/>
+    <hyperlink ref="M31" r:id="rId29" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{E23A26E5-194D-45EA-A2F1-E889B63D07FD}"/>
+    <hyperlink ref="M32" r:id="rId30" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{0E6DB696-497F-4239-A8B7-46C2C5199940}"/>
+    <hyperlink ref="M93" r:id="rId31" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{BB69C920-BAF8-482D-A56C-2AACAB2E77F3}"/>
+    <hyperlink ref="M94" r:id="rId32" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{DE5C1CA5-8732-48F7-AA26-E863829AE35A}"/>
+    <hyperlink ref="M25" r:id="rId33" display="https://www.tandfonline.com/doi/abs/10.2989/1814232X.2012.689623?casa_token=zBny8ik3tAMAAAAA:D-WLZrlhXskUGl1Xag8khGwd83rNrPI2GZ94RlKOsCvfW4t4DDubKDq8PhmhPgZCerNLRIoGbCBZ" xr:uid="{E39ED53A-581E-4853-8724-B65FB994F56E}"/>
+    <hyperlink ref="M33" r:id="rId34" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{A12C861C-DE3B-4BCB-BDBB-F444D3005D50}"/>
+    <hyperlink ref="M34" r:id="rId35" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{51FCF73F-4F9E-4544-833F-8A4663E462E0}"/>
+    <hyperlink ref="M35" r:id="rId36" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{8E2FDF05-C0E0-4302-A9BC-E35AD1195863}"/>
+    <hyperlink ref="M36" r:id="rId37" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{DA47A8DC-CBD4-4F6E-8F7D-4DBAD5984B73}"/>
+    <hyperlink ref="M37" r:id="rId38" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{64CC7A68-9740-4AFF-A8EA-1E78851C1DC7}"/>
+    <hyperlink ref="M38" r:id="rId39" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{83A8139A-8843-40AB-BC27-86520A7C014C}"/>
+    <hyperlink ref="M39" r:id="rId40" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{3144D8CB-3BF2-4634-8BEF-8E89D8093B15}"/>
+    <hyperlink ref="M40" r:id="rId41" location="sec2" display="https://www.sciencedirect.com/science/article/pii/S0278434306003888 - sec2" xr:uid="{BFE72F95-C8B8-4F1E-91DB-ED013D3A4886}"/>
+    <hyperlink ref="M41" r:id="rId42" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2010JC006404" xr:uid="{8EF852C8-50D4-489E-9527-D3A325C052AC}"/>
+    <hyperlink ref="M42" r:id="rId43" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JF001964" xr:uid="{2110E684-38B7-45C5-84F5-E32A08826244}"/>
+    <hyperlink ref="M43" r:id="rId44" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JF001964" xr:uid="{709F131B-7195-4718-B15C-A07FCECC5B84}"/>
+    <hyperlink ref="M44" r:id="rId45" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{6494F74B-3B13-45A7-A29D-FDC5168618CA}"/>
+    <hyperlink ref="M45" r:id="rId46" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{EA759B20-0458-40C9-B195-C0011EB93FD8}"/>
+    <hyperlink ref="M46" r:id="rId47" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{3B1577B0-46A0-4BF5-A255-87797B408296}"/>
+    <hyperlink ref="M47" r:id="rId48" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{82222809-910F-4AA3-9A4A-E3EBA98C6E3A}"/>
+    <hyperlink ref="M48" r:id="rId49" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S0278434313001283 - s0010" xr:uid="{D63B405C-657E-475B-8ECC-C5684644AA81}"/>
+    <hyperlink ref="M49" r:id="rId50" display="https://link.springer.com/article/10.1007/s00190-014-0728-6" xr:uid="{3EB5F2D5-44DC-4D0C-9CF3-1CAE4122D3C1}"/>
+    <hyperlink ref="M50" r:id="rId51" display="https://link.springer.com/article/10.1007/s00190-014-0728-6" xr:uid="{100D97EE-A168-40DA-9DA3-9E17DAA67646}"/>
+    <hyperlink ref="M51" r:id="rId52" display="https://link.springer.com/article/10.1007/s00190-014-0728-6" xr:uid="{1A7EA0BA-2E94-4C73-9514-C3ED80F5D68F}"/>
+    <hyperlink ref="M52" r:id="rId53" display="https://refmar.shom.fr/sites/default/files/2024-07/Reconstruction serie maregraphique Saint-Nazaire par Yann Ferret 2016.pdf" xr:uid="{48F1C5E8-271B-4E1A-8051-89BFC2EF4DBD}"/>
+    <hyperlink ref="M53" r:id="rId54" display="https://refmar.shom.fr/sites/default/files/2024-07/Reconstruction serie maregraphique Saint-Nazaire par Yann Ferret 2016.pdf" xr:uid="{12E3FA0D-A2E7-4C2A-B609-0B888908CDEF}"/>
+    <hyperlink ref="M54" r:id="rId55" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{CC106082-EEF1-418E-85CB-C02B56CCFA6B}"/>
+    <hyperlink ref="M55" r:id="rId56" display="https://theses.hal.science/tel-02899411/" xr:uid="{6A4B93A0-66A0-4293-85EA-8F9F21061263}"/>
+    <hyperlink ref="M56" r:id="rId57" display="https://theses.hal.science/tel-02899411/" xr:uid="{E516641B-7853-4305-B31E-99EB0F5D8024}"/>
+    <hyperlink ref="M57" r:id="rId58" display="https://theses.hal.science/tel-02899411/" xr:uid="{E41ECD23-0035-4CF8-BC5B-D697CB031990}"/>
+    <hyperlink ref="M58" r:id="rId59" display="https://theses.hal.science/tel-02899411/" xr:uid="{319E121D-59E2-4063-AEBC-B830A0345333}"/>
+    <hyperlink ref="M59" r:id="rId60" display="https://theses.hal.science/tel-02899411/" xr:uid="{AC9E7838-2062-49F9-9079-F3EB0389FBC6}"/>
+    <hyperlink ref="M60" r:id="rId61" display="https://theses.hal.science/tel-02899411/" xr:uid="{6FF15F34-5F28-4E20-80B1-69C9ED8F213F}"/>
+    <hyperlink ref="M61" r:id="rId62" display="https://hal.science/hal-04555208v1/file/Khan2023.pdf" xr:uid="{0AA73F62-3AEF-4931-AA1D-6FBEC4CF7591}"/>
+    <hyperlink ref="M62" r:id="rId63" display="https://hal.science/hal-04555208v1/file/Khan2023.pdf" xr:uid="{2CE0289E-388A-4D39-AA63-9BA194C29B33}"/>
+    <hyperlink ref="M63" r:id="rId64" display="https://link.springer.com/article/10.1007/s10236-005-0056-8" xr:uid="{321A9D67-5596-4A40-B002-597D4B83D9EE}"/>
+    <hyperlink ref="M64" r:id="rId65" display="https://link.springer.com/article/10.1007/s10236-013-0598-0" xr:uid="{2DCD71EA-D05F-4583-9D82-705E11770DB0}"/>
+    <hyperlink ref="M65" r:id="rId66" display="https://link.springer.com/article/10.1007/s10236-013-0598-0" xr:uid="{78EA1660-986C-4550-88A7-AD63BD2EC820}"/>
+    <hyperlink ref="M66" r:id="rId67" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{ACACC6AF-8E8B-4E72-AF9D-C38D307C367F}"/>
+    <hyperlink ref="M67" r:id="rId68" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{B6A38606-5207-412A-93F4-0A3D08FFDF3A}"/>
+    <hyperlink ref="M68" r:id="rId69" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{AA47797B-6245-4F5D-9755-8BF33A928639}"/>
+    <hyperlink ref="M69" r:id="rId70" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{352E4836-58F9-4D80-8F88-E85CD1FFC4EF}"/>
+    <hyperlink ref="M70" r:id="rId71" display="https://academic.oup.com/gji/article/71/3/809/656230?login=true" xr:uid="{DAB8DBC4-BC69-4474-A20B-06DEACF6639F}"/>
+    <hyperlink ref="M71" r:id="rId72" location="section2" display="https://os.copernicus.org/articles/17/1623/2021/ - section2" xr:uid="{E7EFF9C5-C900-4089-8209-9E2A773160BE}"/>
+    <hyperlink ref="M72" r:id="rId73" location="section2" display="https://os.copernicus.org/articles/17/1623/2021/ - section2" xr:uid="{F0BB97EB-5B44-430A-83C6-1DDEB69A1ECE}"/>
+    <hyperlink ref="M73" r:id="rId74" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.256" xr:uid="{DE8395E8-1DA0-46AE-B481-D02964E34134}"/>
+    <hyperlink ref="M74" r:id="rId75" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{A0AC456D-CC25-4A97-B3D6-93123EF95A50}"/>
+    <hyperlink ref="M75" r:id="rId76" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{3E5BC94F-EAF2-44FF-8917-B2EFB8AE529D}"/>
+    <hyperlink ref="M76" r:id="rId77" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{E4302009-7369-44AE-80F2-11FFEE46ED4D}"/>
+    <hyperlink ref="M77" r:id="rId78" location="tocto1n3" display="https://journals.openedition.org/mediterranee/170 - tocto1n3" xr:uid="{61032C46-FE99-4D86-B773-6D2F496CFD09}"/>
+    <hyperlink ref="M78" r:id="rId79" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{D1F89FBA-A81A-476D-B3EB-AC18BCFF57E3}"/>
+    <hyperlink ref="M79" r:id="rId80" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{DD2B3EE0-D871-4516-9AC0-F82CEDD540D3}"/>
+    <hyperlink ref="M80" r:id="rId81" location="Sec2" display="https://link.springer.com/article/10.1007/s00190-019-01238-w - Sec2" xr:uid="{E408F5FB-8459-4FC5-A6EC-7060C86DF742}"/>
+    <hyperlink ref="M81" r:id="rId82" display="https://www.scirp.org/journal/paperinformation?paperid=128406" xr:uid="{195D32EE-E070-4B9E-A5BD-B80C3AD86CBE}"/>
+    <hyperlink ref="M82" r:id="rId83" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{903ACD05-5219-4AED-8859-F4714BDE0BB9}"/>
+    <hyperlink ref="M89" r:id="rId84" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{36A32DD3-8E7D-43B7-92C6-ECCC7A0CF09B}"/>
+    <hyperlink ref="M141" r:id="rId85" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{553102E9-CF74-485B-9088-0B3980E0A6C4}"/>
+    <hyperlink ref="M142" r:id="rId86" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{21D13D07-62C9-4C94-BADD-3095560F68A6}"/>
+    <hyperlink ref="M86" r:id="rId87" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2003GL019166" xr:uid="{F04B6DFA-C133-4B48-9EA0-0ECBC803C7FD}"/>
+    <hyperlink ref="M88" r:id="rId88" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{BF360CB9-786B-4C2F-B5F5-3C957D778FAE}"/>
+    <hyperlink ref="M87" r:id="rId89" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{1FED7C96-690E-4D19-85F4-65BB6F23CE17}"/>
+    <hyperlink ref="M85" r:id="rId90" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{3AF75EB3-D702-42B6-BD1B-AFCEB574E447}"/>
+    <hyperlink ref="M84" r:id="rId91" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{C93C2638-FD6B-480E-96F6-8B862C18E451}"/>
+    <hyperlink ref="M83" r:id="rId92" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{1F8F78D0-D119-425A-996A-B08ACE5F35EF}"/>
+    <hyperlink ref="M90" r:id="rId93" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{2099A868-F966-4455-B094-01193B46B861}"/>
+    <hyperlink ref="M91" r:id="rId94" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{46C92736-B19B-4BDA-9BAB-00DC7A4878FC}"/>
+    <hyperlink ref="M92" r:id="rId95" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{EA033195-9E7E-4E07-A0F8-E8E2A0EB6052}"/>
+    <hyperlink ref="M95" r:id="rId96" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{88759562-7CE9-45B6-89B2-9928007923BA}"/>
+    <hyperlink ref="M96" r:id="rId97" location="s0010" display="https://www.sciencedirect.com/science/article/pii/S002216941201092X - s0010" xr:uid="{C57D2CFC-03DE-4A06-BFFA-15ADBEB76026}"/>
+    <hyperlink ref="M100" r:id="rId98" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2011JC007558" xr:uid="{48FCEB4E-3DC3-4808-A7D3-0CD1C40BDE88}"/>
+    <hyperlink ref="M101" r:id="rId99" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377" xr:uid="{59E74865-99AF-4285-BDD6-FE1151B62885}"/>
+    <hyperlink ref="M102" r:id="rId100" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377" xr:uid="{3704BAA3-E61A-419A-9486-009BC900B3F9}"/>
+    <hyperlink ref="M103" r:id="rId101" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/jgrc.20377" xr:uid="{9B3DDBB9-9E35-41F8-AAC3-EE5DF2482932}"/>
+    <hyperlink ref="M104" r:id="rId102" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{9D5353C6-E6BA-4569-9A91-BEF767A13FA1}"/>
+    <hyperlink ref="M105" r:id="rId103" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{AB096B9A-DF1A-491B-9346-4BAE15A4E8B4}"/>
+    <hyperlink ref="M106" r:id="rId104" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{5C45C69D-E6D4-41CE-82A4-49AD3B7540EF}"/>
+    <hyperlink ref="M107" r:id="rId105" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{87CDB602-54EE-4DE0-B155-20D3E0601AFA}"/>
+    <hyperlink ref="M108" r:id="rId106" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{C236D594-1BA2-45E4-98D3-6AB4F1A9030B}"/>
+    <hyperlink ref="M109" r:id="rId107" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{1C31917F-2B22-4CB9-8343-F28F6D080F5D}"/>
+    <hyperlink ref="M110" r:id="rId108" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{E574F02D-1543-407A-985A-3F6153B64E59}"/>
+    <hyperlink ref="M111" r:id="rId109" display="https://rmets.onlinelibrary.wiley.com/doi/full/10.1002/gdj3.112" xr:uid="{1BC07A79-20FB-4C69-A5AE-FCF670F32273}"/>
+    <hyperlink ref="M112" r:id="rId110" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{95DFDDAF-5EFA-4324-9F78-0450A98350F7}"/>
+    <hyperlink ref="M113" r:id="rId111" display="https://www.nodc.noaa.gov/media/pdf/esm/ESM_SEP2003vol14no1.pdf" xr:uid="{3EC24E64-59B0-4A8C-9F05-F5B51E53AD19}"/>
+    <hyperlink ref="M114" r:id="rId112" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{5DC068F5-3CE8-40C8-9390-6BA898E4D60B}"/>
+    <hyperlink ref="M115" r:id="rId113" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{B3144875-5B8C-4B0C-A66D-2FB910C9ED48}"/>
+    <hyperlink ref="M116" r:id="rId114" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{906DD181-D202-46DB-BD3E-A59EB0B27F9F}"/>
+    <hyperlink ref="M117" r:id="rId115" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{B32F09B2-DC8B-4D3B-AA99-28F0D2060362}"/>
+    <hyperlink ref="M118" r:id="rId116" display="https://www.sciencedirect.com/science/article/pii/S0278434309002313" xr:uid="{DC5C2D03-D073-477E-AAB0-7D36DF937E46}"/>
+    <hyperlink ref="M119" r:id="rId117" display="https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010" xr:uid="{FA20EDCB-99D3-416F-B32D-98D067EC1528}"/>
+    <hyperlink ref="M120" r:id="rId118" display="https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010" xr:uid="{92BF6CE4-8982-4D60-A178-3BD1D358316F}"/>
+    <hyperlink ref="M121" r:id="rId119" display="https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010" xr:uid="{76584556-B3A4-485A-97B9-2B5E5BBF9BFD}"/>
+    <hyperlink ref="M122" r:id="rId120" display="https://www.researchgate.net/publication/273705568_Maintaining_legacy_data_Saving_Belfast_Harbour_UK_tide-gauge_data_1901-2010" xr:uid="{E78368A2-EA80-43F2-8026-7BFE601AE1A7}"/>
+    <hyperlink ref="M123" r:id="rId121" display="https://southerncoastalgroup-scopac.org.uk/wp-content/uploads/2022/01/Digitisation-and-Analysis-of-Poole-Harbour-Tide-Gauge-Record-September-2021.pdf" xr:uid="{78A3830A-EFF7-49BC-981A-80F5FCCBC138}"/>
+    <hyperlink ref="M124" r:id="rId122" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{DFD9C9D6-DD4B-4FE5-BBD3-0D5D96D0CDA5}"/>
+    <hyperlink ref="M125" r:id="rId123" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{A53628A9-4972-4871-BCE8-7220B1B21B42}"/>
+    <hyperlink ref="M126" r:id="rId124" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{7A5066A7-A0B3-4B26-A63E-8AE940EA57C5}"/>
+    <hyperlink ref="M127" r:id="rId125" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{79384A48-F27C-4581-B22A-AAB3775BE619}"/>
+    <hyperlink ref="M128" r:id="rId126" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{2D019ABF-696E-4BCD-AF7A-4D54C4765CF6}"/>
+    <hyperlink ref="M129" r:id="rId127" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{A0D30FAD-4CE0-43B0-9344-B667A3F8973F}"/>
+    <hyperlink ref="M130" r:id="rId128" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{E8CC9855-D1E2-4546-AF49-F746ED401ED4}"/>
+    <hyperlink ref="M131" r:id="rId129" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{B2F3BEE8-8054-46B0-B5E2-C6D3E181658B}"/>
+    <hyperlink ref="M132" r:id="rId130" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{C38734CE-3785-4938-8198-1CD9D048C018}"/>
+    <hyperlink ref="M133" r:id="rId131" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{35014EF4-5B31-4E51-A685-1179B635CD90}"/>
+    <hyperlink ref="M134" r:id="rId132" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{8A6519EB-9B30-47C3-88EA-C8B6663D7BBB}"/>
+    <hyperlink ref="M135" r:id="rId133" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{3297DE88-F52A-4DB3-9B4B-1CEB40C7C6E2}"/>
+    <hyperlink ref="M136" r:id="rId134" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{128582CF-DF4B-47AC-9CC7-CD3BDA762D43}"/>
+    <hyperlink ref="M137" r:id="rId135" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{8BD822FB-CC29-4EF8-89DE-F6A00F39693A}"/>
+    <hyperlink ref="M138" r:id="rId136" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{8F73661C-43C0-4DB6-9972-5574995E9389}"/>
+    <hyperlink ref="M139" r:id="rId137" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{8CAA01CB-3909-43E3-B232-C2BFAEBC0BA9}"/>
+    <hyperlink ref="M140" r:id="rId138" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{305EDB46-8346-45CC-9A06-24B18712A9D2}"/>
+    <hyperlink ref="M143" r:id="rId139" display="https://journals.ametsoc.org/view/journals/clim/16/6/1520-0442_2003_016_0982_svatcc_2.0.co_2.xml" xr:uid="{877FE448-F16A-471C-A1E2-F0A16A97D9F8}"/>
+    <hyperlink ref="M144" r:id="rId140" display="https://journals.ametsoc.org/view/journals/clim/16/6/1520-0442_2003_016_0982_svatcc_2.0.co_2.xml" xr:uid="{51D9ADAE-09E1-43D8-92D0-03275242F7F9}"/>
+    <hyperlink ref="M145" r:id="rId141" display="https://journals.ametsoc.org/view/journals/phoc/36/6/jpo2876.1.xml" xr:uid="{9CDE9DF8-CA6E-4BC1-8E17-AE56537524E4}"/>
+    <hyperlink ref="M146" r:id="rId142" display="https://journals.ametsoc.org/view/journals/phoc/36/6/jpo2876.1.xml" xr:uid="{EE13147B-64F9-4C4C-8D7D-0F5A278B8A65}"/>
+    <hyperlink ref="M147" r:id="rId143" display="https://www.researchgate.net/publication/261063515_Nineteenth_Century_North_American_and_Pacific_Tidal_Data_Lost_or_Just_Forgotten" xr:uid="{403D98BC-2040-485D-B445-BAD62F3F7FF3}"/>
+    <hyperlink ref="M148" r:id="rId144" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{AFD017FF-E29F-4FC0-BC0B-FEE844072E07}"/>
+    <hyperlink ref="M149" r:id="rId145" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{6257E5CD-3456-4A59-BCD1-F0A7C4C2A308}"/>
+    <hyperlink ref="M150" r:id="rId146" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{F99C2225-C48A-4B08-96CA-23FE8FED86DB}"/>
+    <hyperlink ref="M151" r:id="rId147" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{B9098E6E-E02E-40C8-BC9A-67200EB7C6A8}"/>
+    <hyperlink ref="M152" r:id="rId148" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2014GL059574" xr:uid="{083BA527-6DB1-4E18-9155-BF949002AF38}"/>
+    <hyperlink ref="M153" r:id="rId149" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2016GL069494" xr:uid="{47809EE2-7636-4718-96DE-F2C5A949A78F}"/>
+    <hyperlink ref="M154" r:id="rId150" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1002/2016GL069494" xr:uid="{8F55C433-CF62-4FC3-829E-9A19363BE8DE}"/>
+    <hyperlink ref="M155" r:id="rId151" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{A9663AAA-58C8-4315-A17E-EE6308CB0EA9}"/>
+    <hyperlink ref="M156" r:id="rId152" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{D802EF92-0129-490C-B79B-154F535F6822}"/>
+    <hyperlink ref="M157" r:id="rId153" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{8FD08862-9501-42DD-AF3D-5099F60354F9}"/>
+    <hyperlink ref="M158" r:id="rId154" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{B233B2D5-C75A-48FA-87F8-59C1978BDBEA}"/>
+    <hyperlink ref="M159" r:id="rId155" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{21FEB18A-FE45-4E97-938B-CD2A2C49DB20}"/>
+    <hyperlink ref="M160" r:id="rId156" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{7D8AC1AA-1439-4E8D-9441-9138EC64A37C}"/>
+    <hyperlink ref="M161" r:id="rId157" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{73693365-73E7-4522-833E-D8832B996757}"/>
+    <hyperlink ref="M162" r:id="rId158" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{D86ABC02-CADD-467E-8962-3881C87DCB43}"/>
+    <hyperlink ref="M163" r:id="rId159" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{AB3955D5-F533-4091-8B76-5AEE00737AD9}"/>
+    <hyperlink ref="M164" r:id="rId160" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{742BF852-41D1-4D24-AF9A-03E290CFA0C5}"/>
+    <hyperlink ref="M165" r:id="rId161" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{7574971D-387E-4A71-8979-D9E8DF0EAB95}"/>
+    <hyperlink ref="M166" r:id="rId162" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{F3E44D40-ABF3-48D9-9970-F4ACDED104DD}"/>
+    <hyperlink ref="M167" r:id="rId163" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{443B5C7F-DB5F-40BC-B5A3-3D4F1E9E8B75}"/>
+    <hyperlink ref="M168" r:id="rId164" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{6B603275-4E3C-440A-A1A3-EC550C7D03C7}"/>
+    <hyperlink ref="M169" r:id="rId165" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{2AB52DAA-F49F-4847-8FAD-5428F0209CB7}"/>
+    <hyperlink ref="M170" r:id="rId166" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{8C1666A9-3A99-4AB9-B5E7-90A57F38A60A}"/>
+    <hyperlink ref="M171" r:id="rId167" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{F1368784-F4C7-4177-8889-A2E8A6A069B7}"/>
+    <hyperlink ref="M172" r:id="rId168" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{20DA0BE9-73B4-4E52-B067-B8C7235C952C}"/>
+    <hyperlink ref="M173" r:id="rId169" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{F47A90A7-57FD-4238-A0FA-EF5CE01F150B}"/>
+    <hyperlink ref="M174" r:id="rId170" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{7332B025-849F-4D0F-A6A0-B68EF897ECA3}"/>
+    <hyperlink ref="M175" r:id="rId171" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{3E658DEA-7C90-4687-AF1C-70161BFFFB03}"/>
+    <hyperlink ref="M176" r:id="rId172" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{76C6D204-67CF-4991-8C41-E42D599276E0}"/>
+    <hyperlink ref="M177" r:id="rId173" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{3318C91F-8FA5-4741-B349-7710C1382305}"/>
+    <hyperlink ref="M178" r:id="rId174" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{56EA06E1-741C-41CD-9F7D-05664FB7D8C8}"/>
+    <hyperlink ref="M179" r:id="rId175" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{7B7CF949-F11F-4233-9ABC-A4FDA8DF9659}"/>
+    <hyperlink ref="M180" r:id="rId176" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{8E59EF75-B158-4167-8CC0-C8EA5786E2F7}"/>
+    <hyperlink ref="M181" r:id="rId177" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{22270271-2763-420D-B695-855454BA4610}"/>
+    <hyperlink ref="M182" r:id="rId178" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{05BD1602-5325-46BC-993B-EEA49B07F123}"/>
+    <hyperlink ref="M183" r:id="rId179" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{CA2F96A4-C0B4-4E3A-8516-88F3580BC3D5}"/>
+    <hyperlink ref="M184" r:id="rId180" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{736CA3FD-E86F-4D9A-B890-08BB06AABAAC}"/>
+    <hyperlink ref="M185" r:id="rId181" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{323CEA39-5EA7-4405-99F2-2C77832558C5}"/>
+    <hyperlink ref="M186" r:id="rId182" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{1A8D548A-2111-4234-9E4A-D414A04B8CD4}"/>
+    <hyperlink ref="M187" r:id="rId183" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{128D16ED-1695-4512-AA8A-55916D65DB84}"/>
+    <hyperlink ref="M188" r:id="rId184" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{EC8DD74A-8421-4C5E-965D-47504ED30A03}"/>
+    <hyperlink ref="M189" r:id="rId185" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{1A730DD5-6A68-4A1B-BB25-9B111035CDA0}"/>
+    <hyperlink ref="M190" r:id="rId186" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{1F9A774E-4B64-42A9-AB3D-DE22F6CDA311}"/>
+    <hyperlink ref="M191" r:id="rId187" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{E6C9F0EA-5951-469D-94B5-FCF489EBC58D}"/>
+    <hyperlink ref="M192" r:id="rId188" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{C92CBB4C-E489-403C-87E4-35A660DF6C47}"/>
+    <hyperlink ref="M193" r:id="rId189" display="https://pdxscholar.library.pdx.edu/cgi/viewcontent.cgi?article=1426&amp;context=cengin_fac" xr:uid="{D00CB8D8-A429-434B-AA25-E6DE9BC2D800}"/>
+    <hyperlink ref="M194" r:id="rId190" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{4C7207D3-04B5-4151-99FC-EF2D5F18B70A}"/>
+    <hyperlink ref="M195" r:id="rId191" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{8F575441-1079-45A1-8671-3BCF62C44985}"/>
+    <hyperlink ref="M196" r:id="rId192" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{E0E404B4-805B-4BEB-BB23-E3957ED793D2}"/>
+    <hyperlink ref="M197" r:id="rId193" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{1D15F609-79E7-4EA8-B52B-B09C10A26149}"/>
+    <hyperlink ref="M198" r:id="rId194" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2017JC013645" xr:uid="{A455A16E-824F-4A21-8E5B-6A69F8DA6D2D}"/>
+    <hyperlink ref="M199" r:id="rId195" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2018JC014313" xr:uid="{90651DDA-1B4E-4E4A-A640-4309F614812C}"/>
+    <hyperlink ref="M200" r:id="rId196" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{E0D3153B-6536-4361-A8CF-90CF167CEB71}"/>
+    <hyperlink ref="M201" r:id="rId197" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{E377A81D-BDA1-417A-83A0-1D6CD249B25D}"/>
+    <hyperlink ref="M202" r:id="rId198" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{06918591-572D-4BDB-B560-4BD1061D66F6}"/>
+    <hyperlink ref="M203" r:id="rId199" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{AD44A2E7-D61F-43B0-BD83-2D3266FF3958}"/>
+    <hyperlink ref="M204" r:id="rId200" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{E0CD3E49-9378-475D-9EF5-6DD71476F6B6}"/>
+    <hyperlink ref="M205" r:id="rId201" display="https://link.springer.com/article/10.1007/s12237-018-0379-6" xr:uid="{A3D2D9E4-0629-413D-8B27-B8769F7B8F8A}"/>
+    <hyperlink ref="M206" r:id="rId202" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{72EA2A2C-2751-403B-A9D9-90102BC30AB9}"/>
+    <hyperlink ref="M207" r:id="rId203" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{B75E343C-2E68-43EB-919E-E74821F55A76}"/>
+    <hyperlink ref="M208" r:id="rId204" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{D13F4EA0-89D0-45AB-B714-77DA9CBE8335}"/>
+    <hyperlink ref="M209" r:id="rId205" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{1A0F1239-8C45-4683-86D4-5D2D736A8A95}"/>
+    <hyperlink ref="M210" r:id="rId206" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{13CE63D3-FA64-4EB7-93C6-3F5034B77228}"/>
+    <hyperlink ref="M211" r:id="rId207" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{695A4B05-709A-4BA3-8F75-4A4AD0FC869C}"/>
+    <hyperlink ref="M212" r:id="rId208" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{EB15D62C-B7D9-4586-9717-F82EF8423798}"/>
+    <hyperlink ref="M213" r:id="rId209" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2019JC015277" xr:uid="{78B21660-03BC-4B7B-A15A-C7CFF8BE01AB}"/>
+    <hyperlink ref="M214" r:id="rId210" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328" xr:uid="{C916C800-315A-421D-AFAF-BEB82D6F42DF}"/>
+    <hyperlink ref="M215" r:id="rId211" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328" xr:uid="{716E0BDF-6307-4DA1-9B51-E9D22A8B8EA7}"/>
+    <hyperlink ref="M216" r:id="rId212" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328" xr:uid="{E80B03DD-9688-4216-9183-E7949FE3CA0D}"/>
+    <hyperlink ref="M217" r:id="rId213" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2020JC016328" xr:uid="{E966F5C6-7EDC-4D08-8DB5-D8104EECB7F1}"/>
+    <hyperlink ref="M218" r:id="rId214" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{53931890-38A4-419B-9C00-A6186ED8E6D5}"/>
+    <hyperlink ref="M219" r:id="rId215" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{06FD2DB5-DD08-4181-A38C-F4F1F5E1B558}"/>
+    <hyperlink ref="M220" r:id="rId216" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{4C0A2094-F5A6-4A7F-8B7E-638BA2D6729A}"/>
+    <hyperlink ref="M221" r:id="rId217" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{18222EC4-4C0C-4290-8CFF-61622546339B}"/>
+    <hyperlink ref="M222" r:id="rId218" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{1B28D095-7256-4B26-9164-BC92052B4C83}"/>
+    <hyperlink ref="M223" r:id="rId219" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{E5789D87-1D40-40E5-8D82-5C640B115195}"/>
+    <hyperlink ref="M224" r:id="rId220" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{19BCF861-2410-496B-AE5F-4562C00BFE33}"/>
+    <hyperlink ref="M225" r:id="rId221" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{D77F3BD6-D314-4CE3-9F24-CB36CDA35D63}"/>
+    <hyperlink ref="M226" r:id="rId222" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{812F1209-D08E-4CCF-8BDF-7116FFB95EB5}"/>
+    <hyperlink ref="M227" r:id="rId223" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{CA1EA76E-5E07-4262-86D6-077B99DB0380}"/>
+    <hyperlink ref="M228" r:id="rId224" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{CBAF28A1-1B94-4B39-808F-B4EB22E4DE8F}"/>
+    <hyperlink ref="M229" r:id="rId225" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{DF7E2030-87C0-4A0D-9375-632DBC1C971A}"/>
+    <hyperlink ref="M230" r:id="rId226" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{041F2026-7E33-442D-BD28-41EAAE88A7B2}"/>
+    <hyperlink ref="M231" r:id="rId227" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{20138437-A8C1-42E7-B8BC-0BF162C944F8}"/>
+    <hyperlink ref="M232" r:id="rId228" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{B4416EA0-03D7-49AF-915F-06AAA2BDD50B}"/>
+    <hyperlink ref="M233" r:id="rId229" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{20D457F4-5776-4759-A342-6118431566CF}"/>
+    <hyperlink ref="M234" r:id="rId230" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{070FBF4F-8098-462A-8919-1CFFB2BC5653}"/>
+    <hyperlink ref="M235" r:id="rId231" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{F6B2AA99-1366-446D-B0D6-3749EB6B5032}"/>
+    <hyperlink ref="M236" r:id="rId232" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{2101F68F-DF2C-4F28-B33B-5C9B588759BB}"/>
+    <hyperlink ref="M237" r:id="rId233" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{A72D5D9D-6114-4869-A293-DFD621B9B36A}"/>
+    <hyperlink ref="M238" r:id="rId234" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{8D6AE4C6-DCBD-4502-BD06-491A4C3A65BB}"/>
+    <hyperlink ref="M239" r:id="rId235" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{B4DABEFA-E8DA-4CD0-AE2B-1068E72CE588}"/>
+    <hyperlink ref="M240" r:id="rId236" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{61A0D4AF-7429-4D20-87E4-8326F0AD4147}"/>
+    <hyperlink ref="M241" r:id="rId237" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{C8951B47-7664-4FCF-8E00-0470D41F3348}"/>
+    <hyperlink ref="M242" r:id="rId238" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{F35891CA-6858-460A-8742-95CA704A0A94}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
